--- a/ICD-O_ICD11_ICD10_correspondance.xlsx
+++ b/ICD-O_ICD11_ICD10_correspondance.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\_5_INFORMATIQUE\_PYTHON\WHO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0948A4B7-AA8B-4854-AF9C-F546C76F248F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{347E7390-C3C5-43F1-98D9-A51FC816A783}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="27855" windowHeight="12810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2014" uniqueCount="915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2058" uniqueCount="920">
   <si>
     <t>ICD-O code</t>
   </si>
@@ -169,9 +169,6 @@
     <t>9961/3</t>
   </si>
   <si>
-    <t>Primary myelofibrosis 9961/3 Primary myelofibrosis, prefibrotic* 9961/3 Primary myelofibrosis, fibrotic*</t>
-  </si>
-  <si>
     <t>2A20.2</t>
   </si>
   <si>
@@ -949,9 +946,6 @@
     <t>9751/1</t>
   </si>
   <si>
-    <t>Langerhans cell histiocytosis NOS 9751/3 Langerhans cell histiocytosis, disseminated</t>
-  </si>
-  <si>
     <t>2B31.2</t>
   </si>
   <si>
@@ -1237,9 +1231,6 @@
     <t>9823/1</t>
   </si>
   <si>
-    <t>Monoclonal B-cell lymphocytosis, CLL type 9591/1 Monoclonal B-cell lymphocytosis, non-CLL type</t>
-  </si>
-  <si>
     <t>4B0Y</t>
   </si>
   <si>
@@ -2765,6 +2756,30 @@
   </si>
   <si>
     <t>2B03.1</t>
+  </si>
+  <si>
+    <t>Primary myelofibrosis, prefibrotic*</t>
+  </si>
+  <si>
+    <t>Primary myelofibrosis, fibrotic*</t>
+  </si>
+  <si>
+    <t>Langerhans cell histiocytosis, disseminated</t>
+  </si>
+  <si>
+    <t>9751/3</t>
+  </si>
+  <si>
+    <t>Monoclonal B-cell lymphocytosis, CLL type</t>
+  </si>
+  <si>
+    <t>Monoclonal B-cell lymphocytosis, non-CLL type</t>
+  </si>
+  <si>
+    <t>9591/1</t>
+  </si>
+  <si>
+    <t>Monoclonal B-cell lymphocytosis, NOS 4B0Y Other specified immune system disorders involving white cell lineages</t>
   </si>
 </sst>
 </file>
@@ -3167,7 +3182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N190"/>
+  <dimension ref="A1:N194"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" style="7" bestFit="1" customWidth="1"/>
@@ -3273,22 +3288,22 @@
         <v>15</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="D3" t="s">
         <v>845</v>
       </c>
-      <c r="D3" t="s">
-        <v>848</v>
-      </c>
       <c r="G3" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3" t="s">
         <v>845</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3" t="s">
-        <v>848</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>19</v>
@@ -3308,31 +3323,31 @@
         <v>15</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D4" t="s">
+        <v>844</v>
+      </c>
+      <c r="G4" t="s">
         <v>847</v>
       </c>
-      <c r="G4" t="s">
-        <v>850</v>
-      </c>
       <c r="H4" s="3" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="I4">
         <v>2</v>
       </c>
       <c r="J4" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="L4" t="s">
         <v>20</v>
       </c>
       <c r="M4" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -3486,6687 +3501,6839 @@
         <v>48</v>
       </c>
       <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" t="s">
         <v>50</v>
       </c>
-      <c r="D9" t="s">
+      <c r="G9" t="s">
         <v>51</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I9">
-        <v>2</v>
-      </c>
-      <c r="J9" t="s">
-        <v>51</v>
-      </c>
-      <c r="K9" s="9" t="s">
+      <c r="L9" t="s">
+        <v>20</v>
+      </c>
+      <c r="M9" t="s">
         <v>53</v>
-      </c>
-      <c r="L9" t="s">
-        <v>20</v>
-      </c>
-      <c r="M9" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>912</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="G10" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="I10">
         <v>2</v>
       </c>
       <c r="J10" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="L10" t="s">
         <v>20</v>
       </c>
       <c r="M10" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>913</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>854</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>853</v>
+        <v>50</v>
       </c>
       <c r="G11" t="s">
-        <v>855</v>
+        <v>51</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>854</v>
+        <v>49</v>
       </c>
       <c r="I11">
         <v>2</v>
       </c>
       <c r="J11" t="s">
-        <v>853</v>
+        <v>50</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="L11" t="s">
         <v>20</v>
       </c>
       <c r="M11" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="G12" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="I12">
         <v>2</v>
       </c>
       <c r="J12" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="L12" t="s">
         <v>20</v>
       </c>
       <c r="M12" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>72</v>
+        <v>851</v>
       </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>850</v>
       </c>
       <c r="G13" t="s">
-        <v>73</v>
+        <v>852</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>72</v>
+        <v>851</v>
       </c>
       <c r="I13">
         <v>2</v>
       </c>
       <c r="J13" t="s">
-        <v>74</v>
+        <v>850</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L13" t="s">
         <v>20</v>
       </c>
       <c r="M13" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>857</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>856</v>
+        <v>63</v>
+      </c>
+      <c r="E14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" t="s">
+        <v>65</v>
       </c>
       <c r="G14" t="s">
-        <v>858</v>
+        <v>66</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>857</v>
+        <v>62</v>
       </c>
       <c r="I14">
         <v>2</v>
       </c>
       <c r="J14" t="s">
-        <v>856</v>
+        <v>63</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="L14" t="s">
         <v>20</v>
       </c>
       <c r="M14" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>865</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>859</v>
+        <v>73</v>
       </c>
       <c r="G15" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="I15">
         <v>2</v>
       </c>
       <c r="J15" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="L15" t="s">
         <v>20</v>
       </c>
       <c r="M15" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B16" t="s">
-        <v>863</v>
+        <v>70</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="D16" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="G16" t="s">
-        <v>867</v>
+        <v>855</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="I16">
         <v>2</v>
       </c>
       <c r="J16" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="K16" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="L16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M16" t="s">
         <v>75</v>
-      </c>
-      <c r="L16" t="s">
-        <v>20</v>
-      </c>
-      <c r="M16" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B17" t="s">
-        <v>869</v>
+        <v>79</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>866</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="G17" t="s">
-        <v>868</v>
+        <v>78</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>866</v>
+        <v>77</v>
       </c>
       <c r="I17">
         <v>2</v>
       </c>
       <c r="J17" t="s">
-        <v>862</v>
+        <v>79</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L17" t="s">
         <v>20</v>
       </c>
       <c r="M17" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>860</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>84</v>
+        <v>858</v>
       </c>
       <c r="D18" t="s">
-        <v>83</v>
+        <v>857</v>
       </c>
       <c r="G18" t="s">
-        <v>85</v>
+        <v>864</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>84</v>
+        <v>858</v>
       </c>
       <c r="I18">
         <v>2</v>
       </c>
       <c r="J18" t="s">
-        <v>83</v>
+        <v>857</v>
       </c>
       <c r="K18" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="L18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M18" t="s">
         <v>75</v>
-      </c>
-      <c r="L18" t="s">
-        <v>20</v>
-      </c>
-      <c r="M18" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>86</v>
+        <v>861</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>866</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>88</v>
+        <v>863</v>
       </c>
       <c r="D19" t="s">
-        <v>89</v>
+        <v>859</v>
       </c>
       <c r="G19" t="s">
-        <v>90</v>
+        <v>865</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>88</v>
+        <v>863</v>
       </c>
       <c r="I19">
         <v>2</v>
       </c>
       <c r="J19" t="s">
-        <v>89</v>
+        <v>859</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="L19" t="s">
         <v>20</v>
       </c>
       <c r="M19" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="G20" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I20">
         <v>2</v>
       </c>
       <c r="J20" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="L20" t="s">
         <v>20</v>
       </c>
       <c r="M20" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G21" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="I21">
         <v>2</v>
       </c>
       <c r="J21" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="L21" t="s">
         <v>20</v>
       </c>
       <c r="M21" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D22" t="s">
-        <v>102</v>
-      </c>
-      <c r="E22" t="s">
-        <v>103</v>
-      </c>
-      <c r="F22" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="G22" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="I22">
         <v>2</v>
       </c>
       <c r="J22" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="L22" t="s">
         <v>20</v>
       </c>
       <c r="M22" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B23" t="s">
         <v>98</v>
       </c>
-      <c r="B23" t="s">
-        <v>108</v>
-      </c>
       <c r="C23" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" t="s">
         <v>95</v>
       </c>
-      <c r="D23" t="s">
+      <c r="G23" t="s">
         <v>96</v>
       </c>
-      <c r="G23" t="s">
-        <v>97</v>
-      </c>
       <c r="H23" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
+      <c r="J23" t="s">
         <v>95</v>
       </c>
-      <c r="I23">
-        <v>2</v>
-      </c>
-      <c r="J23" t="s">
-        <v>96</v>
-      </c>
       <c r="K23" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="L23" t="s">
+        <v>20</v>
+      </c>
+      <c r="M23" t="s">
         <v>68</v>
-      </c>
-      <c r="L23" t="s">
-        <v>20</v>
-      </c>
-      <c r="M23" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="D24" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="E24" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="F24" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="G24" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I24">
         <v>2</v>
       </c>
       <c r="J24" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="L24" t="s">
         <v>20</v>
       </c>
       <c r="M24" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B25" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="G25" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="I25">
         <v>2</v>
       </c>
       <c r="J25" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="L25" t="s">
         <v>20</v>
       </c>
       <c r="M25" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" t="s">
         <v>109</v>
       </c>
-      <c r="B26" t="s">
-        <v>122</v>
-      </c>
       <c r="C26" s="5" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s">
-        <v>120</v>
+        <v>111</v>
+      </c>
+      <c r="E26" t="s">
+        <v>112</v>
+      </c>
+      <c r="F26" t="s">
+        <v>113</v>
       </c>
       <c r="G26" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="I26">
         <v>2</v>
       </c>
       <c r="J26" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="L26" t="s">
         <v>20</v>
       </c>
       <c r="M26" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D27" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="G27" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="I27">
         <v>2</v>
       </c>
       <c r="J27" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="L27" t="s">
         <v>20</v>
       </c>
       <c r="M27" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="B28" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="G28" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="I28">
         <v>2</v>
       </c>
       <c r="J28" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="K28" s="9" t="s">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="L28" t="s">
         <v>20</v>
       </c>
       <c r="M28" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="B29" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="D29" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="G29" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="I29">
         <v>2</v>
       </c>
       <c r="J29" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="L29" t="s">
         <v>20</v>
       </c>
       <c r="M29" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>61</v>
+        <v>127</v>
       </c>
       <c r="B30" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>63</v>
+        <v>129</v>
       </c>
       <c r="D30" t="s">
-        <v>64</v>
+        <v>130</v>
       </c>
       <c r="G30" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>63</v>
+        <v>129</v>
       </c>
       <c r="I30">
         <v>2</v>
       </c>
       <c r="J30" t="s">
-        <v>64</v>
+        <v>132</v>
       </c>
       <c r="K30" s="9" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
       <c r="L30" t="s">
         <v>20</v>
       </c>
       <c r="M30" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>143</v>
+        <v>92</v>
       </c>
       <c r="B31" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="D31" t="s">
-        <v>146</v>
-      </c>
-      <c r="E31" t="s">
-        <v>147</v>
-      </c>
-      <c r="F31" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="G31" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="I31">
         <v>2</v>
       </c>
       <c r="J31" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="L31" t="s">
         <v>20</v>
       </c>
       <c r="M31" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>152</v>
+        <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>145</v>
+        <v>62</v>
       </c>
       <c r="D32" t="s">
-        <v>146</v>
-      </c>
-      <c r="E32" t="s">
-        <v>154</v>
-      </c>
-      <c r="F32" t="s">
-        <v>153</v>
+        <v>63</v>
       </c>
       <c r="G32" t="s">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>145</v>
+        <v>62</v>
       </c>
       <c r="I32">
         <v>2</v>
       </c>
       <c r="J32" t="s">
-        <v>146</v>
+        <v>63</v>
       </c>
       <c r="K32" s="9" t="s">
-        <v>150</v>
+        <v>67</v>
       </c>
       <c r="L32" t="s">
         <v>20</v>
       </c>
       <c r="M32" t="s">
-        <v>151</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="B33" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="C33" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D33" t="s">
         <v>145</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>146</v>
       </c>
+      <c r="F33" t="s">
+        <v>147</v>
+      </c>
       <c r="G33" t="s">
+        <v>148</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I33">
+        <v>2</v>
+      </c>
+      <c r="J33" t="s">
+        <v>145</v>
+      </c>
+      <c r="K33" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I33">
-        <v>2</v>
-      </c>
-      <c r="J33" t="s">
-        <v>146</v>
-      </c>
-      <c r="K33" s="9" t="s">
+      <c r="L33" t="s">
+        <v>20</v>
+      </c>
+      <c r="M33" t="s">
         <v>150</v>
-      </c>
-      <c r="L33" t="s">
-        <v>20</v>
-      </c>
-      <c r="M33" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B34" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C34" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D34" t="s">
         <v>145</v>
       </c>
-      <c r="D34" t="s">
-        <v>146</v>
-      </c>
       <c r="E34" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="F34" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="G34" t="s">
+        <v>148</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I34">
+        <v>2</v>
+      </c>
+      <c r="J34" t="s">
+        <v>145</v>
+      </c>
+      <c r="K34" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="H34" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I34">
-        <v>2</v>
-      </c>
-      <c r="J34" t="s">
-        <v>146</v>
-      </c>
-      <c r="K34" s="9" t="s">
+      <c r="L34" t="s">
+        <v>20</v>
+      </c>
+      <c r="M34" t="s">
         <v>150</v>
-      </c>
-      <c r="L34" t="s">
-        <v>20</v>
-      </c>
-      <c r="M34" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="B35" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C35" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D35" t="s">
         <v>145</v>
       </c>
-      <c r="D35" t="s">
-        <v>146</v>
-      </c>
-      <c r="E35" t="s">
-        <v>163</v>
-      </c>
-      <c r="F35" t="s">
-        <v>164</v>
-      </c>
       <c r="G35" t="s">
+        <v>148</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I35">
+        <v>2</v>
+      </c>
+      <c r="J35" t="s">
+        <v>145</v>
+      </c>
+      <c r="K35" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I35">
-        <v>2</v>
-      </c>
-      <c r="J35" t="s">
-        <v>146</v>
-      </c>
-      <c r="K35" s="9" t="s">
+      <c r="L35" t="s">
+        <v>20</v>
+      </c>
+      <c r="M35" t="s">
         <v>150</v>
-      </c>
-      <c r="L35" t="s">
-        <v>20</v>
-      </c>
-      <c r="M35" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B36" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C36" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D36" t="s">
         <v>145</v>
       </c>
-      <c r="D36" t="s">
-        <v>146</v>
-      </c>
       <c r="E36" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="F36" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G36" t="s">
+        <v>148</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I36">
+        <v>2</v>
+      </c>
+      <c r="J36" t="s">
+        <v>145</v>
+      </c>
+      <c r="K36" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="H36" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I36">
-        <v>2</v>
-      </c>
-      <c r="J36" t="s">
-        <v>146</v>
-      </c>
-      <c r="K36" s="9" t="s">
+      <c r="L36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M36" t="s">
         <v>150</v>
-      </c>
-      <c r="L36" t="s">
-        <v>20</v>
-      </c>
-      <c r="M36" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="B37" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C37" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D37" t="s">
         <v>145</v>
       </c>
-      <c r="D37" t="s">
-        <v>146</v>
-      </c>
       <c r="E37" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="F37" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="G37" t="s">
+        <v>148</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I37">
+        <v>2</v>
+      </c>
+      <c r="J37" t="s">
+        <v>145</v>
+      </c>
+      <c r="K37" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="H37" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I37">
-        <v>2</v>
-      </c>
-      <c r="J37" t="s">
-        <v>146</v>
-      </c>
-      <c r="K37" s="9" t="s">
+      <c r="L37" t="s">
+        <v>20</v>
+      </c>
+      <c r="M37" t="s">
         <v>150</v>
-      </c>
-      <c r="L37" t="s">
-        <v>20</v>
-      </c>
-      <c r="M37" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B38" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="C38" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D38" t="s">
         <v>145</v>
       </c>
-      <c r="D38" t="s">
-        <v>146</v>
-      </c>
       <c r="E38" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="F38" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="G38" t="s">
+        <v>148</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I38">
+        <v>2</v>
+      </c>
+      <c r="J38" t="s">
+        <v>145</v>
+      </c>
+      <c r="K38" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="H38" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I38">
-        <v>2</v>
-      </c>
-      <c r="J38" t="s">
-        <v>146</v>
-      </c>
-      <c r="K38" s="9" t="s">
+      <c r="L38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M38" t="s">
         <v>150</v>
-      </c>
-      <c r="L38" t="s">
-        <v>20</v>
-      </c>
-      <c r="M38" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B39" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C39" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D39" t="s">
         <v>145</v>
       </c>
-      <c r="D39" t="s">
-        <v>146</v>
+      <c r="E39" t="s">
+        <v>170</v>
+      </c>
+      <c r="F39" t="s">
+        <v>171</v>
       </c>
       <c r="G39" t="s">
+        <v>148</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I39">
+        <v>2</v>
+      </c>
+      <c r="J39" t="s">
+        <v>145</v>
+      </c>
+      <c r="K39" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="H39" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I39">
-        <v>2</v>
-      </c>
-      <c r="J39" t="s">
-        <v>146</v>
-      </c>
-      <c r="K39" s="9" t="s">
+      <c r="L39" t="s">
+        <v>20</v>
+      </c>
+      <c r="M39" t="s">
         <v>150</v>
-      </c>
-      <c r="L39" t="s">
-        <v>20</v>
-      </c>
-      <c r="M39" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B40" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C40" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D40" t="s">
         <v>145</v>
       </c>
-      <c r="D40" t="s">
-        <v>146</v>
-      </c>
       <c r="E40" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="F40" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="G40" t="s">
+        <v>148</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I40">
+        <v>2</v>
+      </c>
+      <c r="J40" t="s">
+        <v>145</v>
+      </c>
+      <c r="K40" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="H40" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I40">
-        <v>2</v>
-      </c>
-      <c r="J40" t="s">
-        <v>146</v>
-      </c>
-      <c r="K40" s="9" t="s">
+      <c r="L40" t="s">
+        <v>20</v>
+      </c>
+      <c r="M40" t="s">
         <v>150</v>
-      </c>
-      <c r="L40" t="s">
-        <v>20</v>
-      </c>
-      <c r="M40" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="B41" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C41" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D41" t="s">
         <v>145</v>
       </c>
-      <c r="D41" t="s">
-        <v>146</v>
-      </c>
-      <c r="E41" t="s">
-        <v>185</v>
-      </c>
-      <c r="F41" t="s">
-        <v>186</v>
-      </c>
       <c r="G41" t="s">
+        <v>148</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I41">
+        <v>2</v>
+      </c>
+      <c r="J41" t="s">
+        <v>145</v>
+      </c>
+      <c r="K41" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I41">
-        <v>2</v>
-      </c>
-      <c r="J41" t="s">
-        <v>146</v>
-      </c>
-      <c r="K41" s="9" t="s">
+      <c r="L41" t="s">
+        <v>20</v>
+      </c>
+      <c r="M41" t="s">
         <v>150</v>
-      </c>
-      <c r="L41" t="s">
-        <v>20</v>
-      </c>
-      <c r="M41" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="B42" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>189</v>
+        <v>144</v>
       </c>
       <c r="D42" t="s">
-        <v>190</v>
+        <v>145</v>
+      </c>
+      <c r="E42" t="s">
+        <v>180</v>
+      </c>
+      <c r="F42" t="s">
+        <v>181</v>
       </c>
       <c r="G42" t="s">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>189</v>
+        <v>144</v>
       </c>
       <c r="I42">
         <v>2</v>
       </c>
       <c r="J42" t="s">
-        <v>190</v>
+        <v>145</v>
       </c>
       <c r="K42" s="9" t="s">
-        <v>192</v>
+        <v>149</v>
       </c>
       <c r="L42" t="s">
         <v>20</v>
       </c>
       <c r="M42" t="s">
-        <v>193</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B43" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="C43" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D43" t="s">
         <v>145</v>
       </c>
-      <c r="D43" t="s">
-        <v>146</v>
+      <c r="E43" t="s">
+        <v>184</v>
+      </c>
+      <c r="F43" t="s">
+        <v>185</v>
       </c>
       <c r="G43" t="s">
+        <v>148</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I43">
+        <v>2</v>
+      </c>
+      <c r="J43" t="s">
+        <v>145</v>
+      </c>
+      <c r="K43" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I43">
-        <v>2</v>
-      </c>
-      <c r="J43" t="s">
-        <v>146</v>
-      </c>
-      <c r="K43" s="9" t="s">
+      <c r="L43" t="s">
+        <v>20</v>
+      </c>
+      <c r="M43" t="s">
         <v>150</v>
-      </c>
-      <c r="L43" t="s">
-        <v>20</v>
-      </c>
-      <c r="M43" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="B44" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="D44" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="G44" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="I44">
         <v>2</v>
       </c>
       <c r="J44" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="K44" s="9" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="L44" t="s">
         <v>20</v>
       </c>
       <c r="M44" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="B45" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>204</v>
+        <v>144</v>
       </c>
       <c r="D45" t="s">
-        <v>203</v>
+        <v>145</v>
       </c>
       <c r="G45" t="s">
-        <v>205</v>
+        <v>148</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>204</v>
+        <v>144</v>
       </c>
       <c r="I45">
         <v>2</v>
       </c>
       <c r="J45" t="s">
-        <v>203</v>
+        <v>145</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>200</v>
+        <v>149</v>
       </c>
       <c r="L45" t="s">
         <v>20</v>
       </c>
       <c r="M45" t="s">
-        <v>201</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B46" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="D46" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="G46" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="I46">
         <v>2</v>
       </c>
       <c r="J46" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="K46" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="L46" t="s">
+        <v>20</v>
+      </c>
+      <c r="M46" t="s">
         <v>200</v>
-      </c>
-      <c r="L46" t="s">
-        <v>20</v>
-      </c>
-      <c r="M46" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="B47" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D47" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="G47" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="I47">
         <v>2</v>
       </c>
       <c r="J47" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="K47" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="L47" t="s">
+        <v>20</v>
+      </c>
+      <c r="M47" t="s">
         <v>200</v>
-      </c>
-      <c r="L47" t="s">
-        <v>20</v>
-      </c>
-      <c r="M47" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="B48" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D48" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="G48" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="I48">
         <v>2</v>
       </c>
       <c r="J48" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="K48" s="9" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="L48" t="s">
         <v>20</v>
       </c>
       <c r="M48" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="B49" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="D49" t="s">
-        <v>222</v>
-      </c>
-      <c r="E49" t="s">
-        <v>223</v>
-      </c>
-      <c r="F49" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="G49" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="I49">
         <v>2</v>
       </c>
       <c r="J49" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="K49" s="9" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="L49" t="s">
         <v>20</v>
       </c>
       <c r="M49" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="B50" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="D50" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="G50" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="I50">
         <v>2</v>
       </c>
       <c r="J50" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="K50" s="9" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="L50" t="s">
         <v>20</v>
       </c>
       <c r="M50" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="B51" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="D51" t="s">
-        <v>233</v>
+        <v>221</v>
+      </c>
+      <c r="E51" t="s">
+        <v>222</v>
+      </c>
+      <c r="F51" t="s">
+        <v>219</v>
       </c>
       <c r="G51" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="I51">
         <v>2</v>
       </c>
       <c r="J51" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="K51" s="9" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="L51" t="s">
         <v>20</v>
       </c>
       <c r="M51" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="B52" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="D52" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="G52" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="I52">
         <v>2</v>
       </c>
       <c r="J52" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="K52" s="9" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="L52" t="s">
         <v>20</v>
       </c>
       <c r="M52" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="B53" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="D53" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="G53" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="I53">
         <v>2</v>
       </c>
       <c r="J53" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="K53" s="9" t="s">
-        <v>26</v>
+        <v>235</v>
       </c>
       <c r="L53" t="s">
         <v>20</v>
       </c>
       <c r="M53" t="s">
-        <v>27</v>
+        <v>232</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>870</v>
+        <v>236</v>
       </c>
       <c r="B54" t="s">
-        <v>872</v>
+        <v>237</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>875</v>
+        <v>238</v>
       </c>
       <c r="D54" t="s">
-        <v>874</v>
+        <v>237</v>
       </c>
       <c r="G54" t="s">
-        <v>876</v>
+        <v>239</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>875</v>
+        <v>238</v>
       </c>
       <c r="I54">
         <v>2</v>
       </c>
       <c r="J54" t="s">
-        <v>874</v>
+        <v>237</v>
       </c>
       <c r="K54" s="9" t="s">
-        <v>192</v>
+        <v>240</v>
       </c>
       <c r="L54" t="s">
         <v>20</v>
       </c>
       <c r="M54" t="s">
-        <v>193</v>
+        <v>237</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B55" t="s">
-        <v>871</v>
+        <v>242</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D55" t="s">
-        <v>873</v>
+        <v>244</v>
       </c>
       <c r="G55" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="I55">
         <v>2</v>
       </c>
       <c r="J55" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="K55" s="9" t="s">
-        <v>192</v>
+        <v>26</v>
       </c>
       <c r="L55" t="s">
         <v>20</v>
       </c>
       <c r="M55" t="s">
-        <v>193</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>251</v>
+        <v>867</v>
       </c>
       <c r="B56" t="s">
-        <v>252</v>
+        <v>869</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>253</v>
+        <v>872</v>
       </c>
       <c r="D56" t="s">
-        <v>254</v>
+        <v>871</v>
       </c>
       <c r="G56" t="s">
-        <v>255</v>
+        <v>873</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>253</v>
+        <v>872</v>
       </c>
       <c r="I56">
         <v>2</v>
       </c>
       <c r="J56" t="s">
-        <v>254</v>
+        <v>871</v>
       </c>
       <c r="K56" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="L56" t="s">
+        <v>20</v>
+      </c>
+      <c r="M56" t="s">
         <v>192</v>
-      </c>
-      <c r="L56" t="s">
-        <v>20</v>
-      </c>
-      <c r="M56" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B57" t="s">
-        <v>257</v>
+        <v>868</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="D57" t="s">
-        <v>259</v>
+        <v>870</v>
       </c>
       <c r="G57" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="I57">
         <v>2</v>
       </c>
       <c r="J57" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="K57" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="L57" t="s">
+        <v>20</v>
+      </c>
+      <c r="M57" t="s">
         <v>192</v>
-      </c>
-      <c r="L57" t="s">
-        <v>20</v>
-      </c>
-      <c r="M57" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="B58" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="D58" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="G58" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="I58">
         <v>2</v>
       </c>
       <c r="J58" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="K58" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="L58" t="s">
+        <v>20</v>
+      </c>
+      <c r="M58" t="s">
         <v>192</v>
-      </c>
-      <c r="L58" t="s">
-        <v>20</v>
-      </c>
-      <c r="M58" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="B59" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="D59" t="s">
-        <v>269</v>
+        <v>258</v>
+      </c>
+      <c r="G59" t="s">
+        <v>259</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="I59">
+        <v>2</v>
+      </c>
+      <c r="J59" t="s">
+        <v>258</v>
+      </c>
+      <c r="K59" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="L59" t="s">
+        <v>20</v>
+      </c>
+      <c r="M59" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="B60" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D60" t="s">
-        <v>273</v>
-      </c>
-      <c r="E60" t="s">
-        <v>274</v>
-      </c>
-      <c r="F60" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="G60" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="I60">
         <v>2</v>
       </c>
       <c r="J60" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="K60" s="9" t="s">
-        <v>277</v>
+        <v>191</v>
       </c>
       <c r="L60" t="s">
         <v>20</v>
       </c>
       <c r="M60" t="s">
-        <v>278</v>
+        <v>192</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="B61" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="D61" t="s">
-        <v>273</v>
-      </c>
-      <c r="E61" t="s">
-        <v>281</v>
-      </c>
-      <c r="F61" t="s">
-        <v>282</v>
-      </c>
-      <c r="G61" t="s">
-        <v>276</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="I61">
-        <v>2</v>
-      </c>
-      <c r="J61" t="s">
-        <v>273</v>
-      </c>
-      <c r="K61" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="L61" t="s">
-        <v>20</v>
-      </c>
-      <c r="M61" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="B62" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="C62" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="D62" t="s">
         <v>272</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>273</v>
       </c>
+      <c r="F62" t="s">
+        <v>274</v>
+      </c>
       <c r="G62" t="s">
+        <v>275</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="I62">
+        <v>2</v>
+      </c>
+      <c r="J62" t="s">
+        <v>272</v>
+      </c>
+      <c r="K62" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="I62">
-        <v>2</v>
-      </c>
-      <c r="J62" t="s">
-        <v>273</v>
-      </c>
-      <c r="K62" s="9" t="s">
+      <c r="L62" t="s">
+        <v>20</v>
+      </c>
+      <c r="M62" t="s">
         <v>277</v>
-      </c>
-      <c r="L62" t="s">
-        <v>20</v>
-      </c>
-      <c r="M62" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B63" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C63" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="D63" t="s">
         <v>272</v>
       </c>
-      <c r="D63" t="s">
-        <v>273</v>
-      </c>
       <c r="E63" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="F63" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="G63" t="s">
+        <v>275</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="I63">
+        <v>2</v>
+      </c>
+      <c r="J63" t="s">
+        <v>272</v>
+      </c>
+      <c r="K63" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="H63" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="I63">
-        <v>2</v>
-      </c>
-      <c r="J63" t="s">
-        <v>273</v>
-      </c>
-      <c r="K63" s="9" t="s">
+      <c r="L63" t="s">
+        <v>20</v>
+      </c>
+      <c r="M63" t="s">
         <v>277</v>
-      </c>
-      <c r="L63" t="s">
-        <v>20</v>
-      </c>
-      <c r="M63" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B64" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="C64" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="D64" t="s">
         <v>272</v>
       </c>
-      <c r="D64" t="s">
-        <v>273</v>
-      </c>
-      <c r="E64" t="s">
-        <v>291</v>
-      </c>
-      <c r="F64" t="s">
-        <v>292</v>
-      </c>
       <c r="G64" t="s">
+        <v>275</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="I64">
+        <v>2</v>
+      </c>
+      <c r="J64" t="s">
+        <v>272</v>
+      </c>
+      <c r="K64" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="H64" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="I64">
-        <v>2</v>
-      </c>
-      <c r="J64" t="s">
-        <v>273</v>
-      </c>
-      <c r="K64" s="9" t="s">
+      <c r="L64" t="s">
+        <v>20</v>
+      </c>
+      <c r="M64" t="s">
         <v>277</v>
-      </c>
-      <c r="L64" t="s">
-        <v>20</v>
-      </c>
-      <c r="M64" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B65" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C65" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="D65" t="s">
         <v>272</v>
       </c>
-      <c r="D65" t="s">
-        <v>273</v>
+      <c r="E65" t="s">
+        <v>286</v>
+      </c>
+      <c r="F65" t="s">
+        <v>287</v>
       </c>
       <c r="G65" t="s">
+        <v>275</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="I65">
+        <v>2</v>
+      </c>
+      <c r="J65" t="s">
+        <v>272</v>
+      </c>
+      <c r="K65" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="H65" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="I65">
-        <v>2</v>
-      </c>
-      <c r="J65" t="s">
-        <v>273</v>
-      </c>
-      <c r="K65" s="9" t="s">
+      <c r="L65" t="s">
+        <v>20</v>
+      </c>
+      <c r="M65" t="s">
         <v>277</v>
-      </c>
-      <c r="L65" t="s">
-        <v>20</v>
-      </c>
-      <c r="M65" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B66" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C66" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="D66" t="s">
         <v>272</v>
       </c>
-      <c r="D66" t="s">
-        <v>273</v>
+      <c r="E66" t="s">
+        <v>290</v>
+      </c>
+      <c r="F66" t="s">
+        <v>291</v>
       </c>
       <c r="G66" t="s">
+        <v>275</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="I66">
+        <v>2</v>
+      </c>
+      <c r="J66" t="s">
+        <v>272</v>
+      </c>
+      <c r="K66" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="I66">
-        <v>2</v>
-      </c>
-      <c r="J66" t="s">
-        <v>273</v>
-      </c>
-      <c r="K66" s="9" t="s">
+      <c r="L66" t="s">
+        <v>20</v>
+      </c>
+      <c r="M66" t="s">
         <v>277</v>
-      </c>
-      <c r="L66" t="s">
-        <v>20</v>
-      </c>
-      <c r="M66" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="B67" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="D67" t="s">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="G67" t="s">
-        <v>299</v>
+        <v>275</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="I67">
         <v>2</v>
       </c>
       <c r="J67" t="s">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="K67" s="9" t="s">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="L67" t="s">
         <v>20</v>
       </c>
       <c r="M67" t="s">
-        <v>301</v>
+        <v>277</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="B68" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="D68" t="s">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="G68" t="s">
-        <v>305</v>
+        <v>275</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="I68">
         <v>2</v>
       </c>
       <c r="J68" t="s">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="K68" s="9" t="s">
-        <v>306</v>
+        <v>276</v>
       </c>
       <c r="L68" t="s">
         <v>20</v>
       </c>
       <c r="M68" t="s">
-        <v>307</v>
+        <v>277</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="B69" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="D69" t="s">
-        <v>311</v>
-      </c>
-      <c r="E69" t="s">
-        <v>312</v>
-      </c>
-      <c r="F69" t="s">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="G69" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="I69">
         <v>2</v>
       </c>
       <c r="J69" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="K69" s="9" t="s">
-        <v>68</v>
+        <v>299</v>
       </c>
       <c r="L69" t="s">
         <v>20</v>
       </c>
       <c r="M69" t="s">
-        <v>69</v>
+        <v>300</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="B70" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="D70" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="G70" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="I70">
         <v>2</v>
       </c>
       <c r="J70" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="K70" s="9" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="L70" t="s">
         <v>20</v>
       </c>
       <c r="M70" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="B71" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="D71" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="E71" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="F71" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="G71" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="I71">
         <v>2</v>
       </c>
       <c r="J71" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="K71" s="9" t="s">
-        <v>319</v>
+        <v>67</v>
       </c>
       <c r="L71" t="s">
         <v>20</v>
       </c>
       <c r="M71" t="s">
-        <v>320</v>
+        <v>68</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>321</v>
+        <v>915</v>
       </c>
       <c r="B72" t="s">
-        <v>327</v>
+        <v>914</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="D72" t="s">
-        <v>327</v>
+        <v>309</v>
+      </c>
+      <c r="E72" t="s">
+        <v>310</v>
+      </c>
+      <c r="F72" t="s">
+        <v>311</v>
       </c>
       <c r="G72" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="I72">
         <v>2</v>
       </c>
       <c r="J72" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="K72" s="9" t="s">
-        <v>319</v>
+        <v>67</v>
       </c>
       <c r="L72" t="s">
         <v>20</v>
       </c>
       <c r="M72" t="s">
-        <v>320</v>
+        <v>68</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="B73" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="D73" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="G73" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="I73">
         <v>2</v>
       </c>
       <c r="J73" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="K73" s="9" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="L73" t="s">
-        <v>335</v>
+        <v>20</v>
       </c>
       <c r="M73" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="B74" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="D74" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="E74" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="F74" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="G74" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="I74">
         <v>2</v>
       </c>
       <c r="J74" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="K74" s="9" t="s">
-        <v>68</v>
+        <v>317</v>
       </c>
       <c r="L74" t="s">
         <v>20</v>
       </c>
       <c r="M74" t="s">
-        <v>69</v>
+        <v>318</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="B75" t="s">
-        <v>343</v>
+        <v>325</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="D75" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="G75" t="s">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="I75">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J75" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="K75" s="9" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="L75" t="s">
-        <v>335</v>
+        <v>20</v>
       </c>
       <c r="M75" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="B76" t="s">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="D76" t="s">
-        <v>345</v>
+        <v>329</v>
       </c>
       <c r="G76" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="I76">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J76" t="s">
-        <v>345</v>
+        <v>329</v>
       </c>
       <c r="K76" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="L76" t="s">
+        <v>333</v>
+      </c>
+      <c r="M76" t="s">
         <v>334</v>
-      </c>
-      <c r="L76" t="s">
-        <v>335</v>
-      </c>
-      <c r="M76" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B77" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="D77" t="s">
-        <v>350</v>
+        <v>338</v>
+      </c>
+      <c r="E77" t="s">
+        <v>339</v>
+      </c>
+      <c r="F77" t="s">
+        <v>336</v>
       </c>
       <c r="G77" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="I77">
         <v>2</v>
       </c>
       <c r="J77" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="K77" s="9" t="s">
-        <v>353</v>
+        <v>67</v>
       </c>
       <c r="L77" t="s">
         <v>20</v>
       </c>
       <c r="M77" t="s">
-        <v>350</v>
+        <v>68</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>354</v>
+        <v>335</v>
       </c>
       <c r="B78" t="s">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="D78" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="G78" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="I78">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J78" t="s">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="K78" s="9" t="s">
-        <v>68</v>
+        <v>332</v>
       </c>
       <c r="L78" t="s">
-        <v>20</v>
+        <v>333</v>
       </c>
       <c r="M78" t="s">
-        <v>69</v>
+        <v>334</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="B79" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="D79" t="s">
-        <v>363</v>
-      </c>
-      <c r="E79" t="s">
-        <v>364</v>
-      </c>
-      <c r="F79" t="s">
-        <v>365</v>
+        <v>343</v>
       </c>
       <c r="G79" t="s">
-        <v>366</v>
+        <v>344</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="I79">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J79" t="s">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="K79" s="9" t="s">
-        <v>68</v>
+        <v>332</v>
       </c>
       <c r="L79" t="s">
-        <v>20</v>
+        <v>333</v>
       </c>
       <c r="M79" t="s">
-        <v>69</v>
+        <v>334</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="B80" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="D80" t="s">
-        <v>363</v>
-      </c>
-      <c r="E80" t="s">
-        <v>369</v>
-      </c>
-      <c r="F80" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
       <c r="G80" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="I80">
         <v>2</v>
       </c>
       <c r="J80" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="K80" s="9" t="s">
-        <v>68</v>
+        <v>351</v>
       </c>
       <c r="L80" t="s">
         <v>20</v>
       </c>
       <c r="M80" t="s">
-        <v>69</v>
+        <v>348</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="B81" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="D81" t="s">
-        <v>363</v>
-      </c>
-      <c r="E81" t="s">
-        <v>373</v>
-      </c>
-      <c r="F81" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="G81" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="I81">
         <v>2</v>
       </c>
       <c r="J81" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="K81" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="L81" t="s">
+        <v>20</v>
+      </c>
+      <c r="M81" t="s">
         <v>68</v>
-      </c>
-      <c r="L81" t="s">
-        <v>20</v>
-      </c>
-      <c r="M81" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="B82" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D82" t="s">
-        <v>377</v>
+        <v>361</v>
+      </c>
+      <c r="E82" t="s">
+        <v>362</v>
+      </c>
+      <c r="F82" t="s">
+        <v>363</v>
       </c>
       <c r="G82" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="I82">
         <v>2</v>
       </c>
       <c r="J82" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="K82" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="L82" t="s">
+        <v>20</v>
+      </c>
+      <c r="M82" t="s">
         <v>68</v>
-      </c>
-      <c r="L82" t="s">
-        <v>20</v>
-      </c>
-      <c r="M82" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="B83" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D83" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E83" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="F83" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="G83" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="I83">
         <v>2</v>
       </c>
       <c r="J83" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="K83" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="L83" t="s">
+        <v>20</v>
+      </c>
+      <c r="M83" t="s">
         <v>68</v>
-      </c>
-      <c r="L83" t="s">
-        <v>20</v>
-      </c>
-      <c r="M83" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="B84" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D84" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E84" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="F84" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
       <c r="G84" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="I84">
         <v>2</v>
       </c>
       <c r="J84" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="K84" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="L84" t="s">
+        <v>20</v>
+      </c>
+      <c r="M84" t="s">
         <v>68</v>
-      </c>
-      <c r="L84" t="s">
-        <v>20</v>
-      </c>
-      <c r="M84" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="B85" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="D85" t="s">
-        <v>363</v>
-      </c>
-      <c r="E85" t="s">
-        <v>389</v>
-      </c>
-      <c r="F85" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="G85" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="I85">
         <v>2</v>
       </c>
       <c r="J85" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="K85" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="L85" t="s">
+        <v>20</v>
+      </c>
+      <c r="M85" t="s">
         <v>68</v>
-      </c>
-      <c r="L85" t="s">
-        <v>20</v>
-      </c>
-      <c r="M85" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="B86" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>145</v>
+        <v>360</v>
       </c>
       <c r="D86" t="s">
-        <v>146</v>
+        <v>361</v>
+      </c>
+      <c r="E86" t="s">
+        <v>379</v>
+      </c>
+      <c r="F86" t="s">
+        <v>380</v>
       </c>
       <c r="G86" t="s">
-        <v>149</v>
+        <v>364</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>145</v>
+        <v>360</v>
       </c>
       <c r="I86">
         <v>2</v>
       </c>
       <c r="J86" t="s">
-        <v>146</v>
+        <v>361</v>
       </c>
       <c r="K86" s="9" t="s">
-        <v>150</v>
+        <v>67</v>
       </c>
       <c r="L86" t="s">
         <v>20</v>
       </c>
       <c r="M86" t="s">
-        <v>151</v>
+        <v>68</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="B87" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D87" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E87" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="F87" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="G87" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="I87">
         <v>2</v>
       </c>
       <c r="J87" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="K87" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="L87" t="s">
+        <v>20</v>
+      </c>
+      <c r="M87" t="s">
         <v>68</v>
-      </c>
-      <c r="L87" t="s">
-        <v>20</v>
-      </c>
-      <c r="M87" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="B88" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D88" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E88" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="F88" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="G88" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="I88">
         <v>2</v>
       </c>
       <c r="J88" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="K88" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="L88" t="s">
+        <v>20</v>
+      </c>
+      <c r="M88" t="s">
         <v>68</v>
-      </c>
-      <c r="L88" t="s">
-        <v>20</v>
-      </c>
-      <c r="M88" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B89" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>362</v>
+        <v>144</v>
       </c>
       <c r="D89" t="s">
-        <v>363</v>
+        <v>145</v>
       </c>
       <c r="G89" t="s">
-        <v>366</v>
+        <v>148</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>362</v>
+        <v>144</v>
       </c>
       <c r="I89">
         <v>2</v>
       </c>
       <c r="J89" t="s">
-        <v>363</v>
+        <v>145</v>
       </c>
       <c r="K89" s="9" t="s">
-        <v>68</v>
+        <v>149</v>
       </c>
       <c r="L89" t="s">
         <v>20</v>
       </c>
       <c r="M89" t="s">
-        <v>69</v>
+        <v>150</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
-        <v>371</v>
+        <v>391</v>
       </c>
       <c r="B90" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D90" t="s">
-        <v>363</v>
+        <v>361</v>
+      </c>
+      <c r="E90" t="s">
+        <v>393</v>
+      </c>
+      <c r="F90" t="s">
+        <v>394</v>
       </c>
       <c r="G90" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="I90">
         <v>2</v>
       </c>
       <c r="J90" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="K90" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="L90" t="s">
+        <v>20</v>
+      </c>
+      <c r="M90" t="s">
         <v>68</v>
-      </c>
-      <c r="L90" t="s">
-        <v>20</v>
-      </c>
-      <c r="M90" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>354</v>
+        <v>395</v>
       </c>
       <c r="B91" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="D91" t="s">
-        <v>357</v>
+        <v>361</v>
+      </c>
+      <c r="E91" t="s">
+        <v>397</v>
+      </c>
+      <c r="F91" t="s">
+        <v>398</v>
       </c>
       <c r="G91" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="I91">
         <v>2</v>
       </c>
       <c r="J91" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K91" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="L91" t="s">
+        <v>20</v>
+      </c>
+      <c r="M91" t="s">
         <v>68</v>
-      </c>
-      <c r="L91" t="s">
-        <v>20</v>
-      </c>
-      <c r="M91" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="B92" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>406</v>
+        <v>360</v>
       </c>
       <c r="D92" t="s">
-        <v>407</v>
-      </c>
-      <c r="E92" t="s">
-        <v>408</v>
-      </c>
-      <c r="F92" t="s">
-        <v>409</v>
+        <v>361</v>
       </c>
       <c r="G92" t="s">
-        <v>410</v>
+        <v>364</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>406</v>
+        <v>360</v>
       </c>
       <c r="I92">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J92" t="s">
-        <v>407</v>
+        <v>361</v>
       </c>
       <c r="K92" s="9" t="s">
-        <v>411</v>
+        <v>67</v>
       </c>
       <c r="L92" t="s">
-        <v>335</v>
+        <v>20</v>
       </c>
       <c r="M92" t="s">
-        <v>412</v>
+        <v>68</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>413</v>
+        <v>369</v>
       </c>
       <c r="B93" t="s">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>415</v>
+        <v>360</v>
       </c>
       <c r="D93" t="s">
-        <v>416</v>
+        <v>361</v>
       </c>
       <c r="G93" t="s">
-        <v>417</v>
+        <v>364</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>415</v>
+        <v>360</v>
       </c>
       <c r="I93">
         <v>2</v>
       </c>
       <c r="J93" t="s">
-        <v>416</v>
+        <v>361</v>
       </c>
       <c r="K93" s="9" t="s">
-        <v>418</v>
+        <v>67</v>
       </c>
       <c r="L93" t="s">
         <v>20</v>
       </c>
       <c r="M93" t="s">
-        <v>419</v>
+        <v>68</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
-        <v>420</v>
+        <v>352</v>
       </c>
       <c r="B94" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>422</v>
+        <v>354</v>
       </c>
       <c r="D94" t="s">
-        <v>423</v>
+        <v>355</v>
       </c>
       <c r="G94" t="s">
-        <v>424</v>
+        <v>356</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>422</v>
+        <v>354</v>
       </c>
       <c r="I94">
         <v>2</v>
       </c>
       <c r="J94" t="s">
-        <v>423</v>
+        <v>357</v>
       </c>
       <c r="K94" s="9" t="s">
-        <v>425</v>
+        <v>67</v>
       </c>
       <c r="L94" t="s">
         <v>20</v>
       </c>
       <c r="M94" t="s">
-        <v>423</v>
+        <v>68</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>426</v>
+        <v>402</v>
       </c>
       <c r="B95" t="s">
-        <v>427</v>
+        <v>916</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>428</v>
+        <v>403</v>
       </c>
       <c r="D95" t="s">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E95" t="s">
-        <v>430</v>
+        <v>405</v>
       </c>
       <c r="F95" t="s">
-        <v>431</v>
+        <v>919</v>
       </c>
       <c r="G95" t="s">
-        <v>432</v>
+        <v>407</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>428</v>
+        <v>403</v>
       </c>
       <c r="I95">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J95" t="s">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="K95" s="9" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="L95" t="s">
-        <v>20</v>
+        <v>333</v>
       </c>
       <c r="M95" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
-        <v>433</v>
+        <v>918</v>
       </c>
       <c r="B96" t="s">
-        <v>434</v>
+        <v>917</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>428</v>
+        <v>403</v>
       </c>
       <c r="D96" t="s">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E96" t="s">
-        <v>435</v>
+        <v>405</v>
       </c>
       <c r="F96" t="s">
-        <v>434</v>
+        <v>406</v>
       </c>
       <c r="G96" t="s">
-        <v>432</v>
+        <v>407</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>428</v>
+        <v>403</v>
       </c>
       <c r="I96">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J96" t="s">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="K96" s="9" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="L96" t="s">
-        <v>20</v>
+        <v>333</v>
       </c>
       <c r="M96" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>433</v>
+        <v>410</v>
       </c>
       <c r="B97" t="s">
-        <v>436</v>
+        <v>411</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>437</v>
+        <v>412</v>
       </c>
       <c r="D97" t="s">
-        <v>438</v>
-      </c>
-      <c r="E97" t="s">
-        <v>439</v>
-      </c>
-      <c r="F97" t="s">
-        <v>440</v>
+        <v>413</v>
       </c>
       <c r="G97" t="s">
-        <v>441</v>
+        <v>414</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>437</v>
+        <v>412</v>
       </c>
       <c r="I97">
         <v>2</v>
       </c>
       <c r="J97" t="s">
-        <v>438</v>
+        <v>413</v>
       </c>
       <c r="K97" s="9" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="L97" t="s">
         <v>20</v>
       </c>
       <c r="M97" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
-        <v>442</v>
+        <v>417</v>
       </c>
       <c r="B98" t="s">
-        <v>443</v>
+        <v>418</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>444</v>
+        <v>419</v>
       </c>
       <c r="D98" t="s">
-        <v>443</v>
+        <v>420</v>
       </c>
       <c r="G98" t="s">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>444</v>
+        <v>419</v>
       </c>
       <c r="I98">
         <v>2</v>
       </c>
       <c r="J98" t="s">
-        <v>443</v>
+        <v>420</v>
       </c>
       <c r="K98" s="9" t="s">
-        <v>446</v>
+        <v>422</v>
       </c>
       <c r="L98" t="s">
         <v>20</v>
       </c>
       <c r="M98" t="s">
-        <v>447</v>
+        <v>420</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>448</v>
+        <v>423</v>
       </c>
       <c r="B99" t="s">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="D99" t="s">
-        <v>451</v>
+        <v>426</v>
       </c>
       <c r="E99" t="s">
-        <v>452</v>
+        <v>427</v>
       </c>
       <c r="F99" t="s">
-        <v>449</v>
+        <v>428</v>
       </c>
       <c r="G99" t="s">
-        <v>453</v>
+        <v>429</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="I99">
         <v>2</v>
       </c>
       <c r="J99" t="s">
-        <v>451</v>
+        <v>426</v>
       </c>
       <c r="K99" s="9" t="s">
-        <v>454</v>
+        <v>415</v>
       </c>
       <c r="L99" t="s">
         <v>20</v>
       </c>
       <c r="M99" t="s">
-        <v>455</v>
+        <v>416</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="B100" t="s">
-        <v>456</v>
+        <v>431</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>457</v>
+        <v>425</v>
       </c>
       <c r="D100" t="s">
-        <v>458</v>
+        <v>426</v>
+      </c>
+      <c r="E100" t="s">
+        <v>432</v>
+      </c>
+      <c r="F100" t="s">
+        <v>431</v>
       </c>
       <c r="G100" t="s">
-        <v>459</v>
+        <v>429</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>457</v>
+        <v>425</v>
       </c>
       <c r="I100">
         <v>2</v>
       </c>
       <c r="J100" t="s">
-        <v>458</v>
+        <v>426</v>
       </c>
       <c r="K100" s="9" t="s">
-        <v>460</v>
+        <v>415</v>
       </c>
       <c r="L100" t="s">
         <v>20</v>
       </c>
       <c r="M100" t="s">
-        <v>461</v>
+        <v>416</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="B101" t="s">
-        <v>462</v>
+        <v>433</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>463</v>
+        <v>434</v>
       </c>
       <c r="D101" t="s">
-        <v>462</v>
+        <v>435</v>
+      </c>
+      <c r="E101" t="s">
+        <v>436</v>
+      </c>
+      <c r="F101" t="s">
+        <v>437</v>
       </c>
       <c r="G101" t="s">
-        <v>464</v>
+        <v>438</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>463</v>
+        <v>434</v>
       </c>
       <c r="I101">
         <v>2</v>
       </c>
       <c r="J101" t="s">
-        <v>462</v>
+        <v>435</v>
       </c>
       <c r="K101" s="9" t="s">
-        <v>460</v>
+        <v>415</v>
       </c>
       <c r="L101" t="s">
         <v>20</v>
       </c>
       <c r="M101" t="s">
-        <v>461</v>
+        <v>416</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="B102" t="s">
-        <v>465</v>
+        <v>440</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>466</v>
+        <v>441</v>
       </c>
       <c r="D102" t="s">
-        <v>467</v>
+        <v>440</v>
       </c>
       <c r="G102" t="s">
-        <v>468</v>
+        <v>442</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>466</v>
+        <v>441</v>
       </c>
       <c r="I102">
         <v>2</v>
       </c>
       <c r="J102" t="s">
-        <v>467</v>
+        <v>440</v>
       </c>
       <c r="K102" s="9" t="s">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="L102" t="s">
         <v>20</v>
       </c>
       <c r="M102" t="s">
-        <v>470</v>
+        <v>444</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="B103" t="s">
-        <v>472</v>
+        <v>446</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>473</v>
+        <v>447</v>
       </c>
       <c r="D103" t="s">
-        <v>474</v>
+        <v>448</v>
+      </c>
+      <c r="E103" t="s">
+        <v>449</v>
+      </c>
+      <c r="F103" t="s">
+        <v>446</v>
       </c>
       <c r="G103" t="s">
-        <v>475</v>
+        <v>450</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>473</v>
+        <v>447</v>
       </c>
       <c r="I103">
         <v>2</v>
       </c>
       <c r="J103" t="s">
-        <v>474</v>
+        <v>448</v>
       </c>
       <c r="K103" s="9" t="s">
-        <v>476</v>
+        <v>451</v>
       </c>
       <c r="L103" t="s">
         <v>20</v>
       </c>
       <c r="M103" t="s">
-        <v>477</v>
+        <v>452</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
-        <v>478</v>
+        <v>445</v>
       </c>
       <c r="B104" t="s">
-        <v>479</v>
+        <v>453</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>480</v>
+        <v>454</v>
       </c>
       <c r="D104" t="s">
-        <v>479</v>
+        <v>455</v>
       </c>
       <c r="G104" t="s">
-        <v>481</v>
+        <v>456</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>480</v>
+        <v>454</v>
       </c>
       <c r="I104">
         <v>2</v>
       </c>
       <c r="J104" t="s">
-        <v>479</v>
+        <v>455</v>
       </c>
       <c r="K104" s="9" t="s">
-        <v>476</v>
+        <v>457</v>
       </c>
       <c r="L104" t="s">
         <v>20</v>
       </c>
       <c r="M104" t="s">
-        <v>477</v>
+        <v>458</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>478</v>
+        <v>445</v>
       </c>
       <c r="B105" t="s">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>483</v>
+        <v>460</v>
       </c>
       <c r="D105" t="s">
-        <v>484</v>
-      </c>
-      <c r="E105" t="s">
-        <v>485</v>
-      </c>
-      <c r="F105" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="G105" t="s">
-        <v>487</v>
+        <v>461</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>483</v>
+        <v>460</v>
       </c>
       <c r="I105">
         <v>2</v>
       </c>
       <c r="J105" t="s">
-        <v>484</v>
+        <v>459</v>
       </c>
       <c r="K105" s="9" t="s">
-        <v>476</v>
+        <v>457</v>
       </c>
       <c r="L105" t="s">
         <v>20</v>
       </c>
       <c r="M105" t="s">
-        <v>477</v>
+        <v>458</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
-        <v>488</v>
+        <v>445</v>
       </c>
       <c r="B106" t="s">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
       <c r="D106" t="s">
-        <v>491</v>
-      </c>
-      <c r="E106" t="s">
-        <v>492</v>
-      </c>
-      <c r="F106" t="s">
-        <v>493</v>
+        <v>464</v>
       </c>
       <c r="G106" t="s">
-        <v>494</v>
+        <v>465</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
       <c r="I106">
         <v>2</v>
       </c>
       <c r="J106" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="K106" s="9" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="L106" t="s">
         <v>20</v>
       </c>
       <c r="M106" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>495</v>
+        <v>468</v>
       </c>
       <c r="B107" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>497</v>
+        <v>470</v>
       </c>
       <c r="D107" t="s">
-        <v>496</v>
+        <v>471</v>
       </c>
       <c r="G107" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>497</v>
+        <v>470</v>
       </c>
       <c r="I107">
         <v>2</v>
       </c>
       <c r="J107" t="s">
-        <v>496</v>
+        <v>471</v>
       </c>
       <c r="K107" s="9" t="s">
-        <v>499</v>
+        <v>473</v>
       </c>
       <c r="L107" t="s">
         <v>20</v>
       </c>
       <c r="M107" t="s">
-        <v>500</v>
+        <v>474</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
-        <v>501</v>
+        <v>475</v>
       </c>
       <c r="B108" t="s">
-        <v>502</v>
+        <v>476</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>503</v>
+        <v>477</v>
       </c>
       <c r="D108" t="s">
-        <v>504</v>
-      </c>
-      <c r="E108" t="s">
-        <v>505</v>
-      </c>
-      <c r="F108" t="s">
-        <v>506</v>
+        <v>476</v>
       </c>
       <c r="G108" t="s">
-        <v>507</v>
+        <v>478</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>503</v>
+        <v>477</v>
       </c>
       <c r="I108">
         <v>2</v>
       </c>
       <c r="J108" t="s">
-        <v>504</v>
+        <v>476</v>
       </c>
       <c r="K108" s="9" t="s">
-        <v>508</v>
+        <v>473</v>
       </c>
       <c r="L108" t="s">
         <v>20</v>
       </c>
       <c r="M108" t="s">
-        <v>504</v>
+        <v>474</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>509</v>
+        <v>475</v>
       </c>
       <c r="B109" t="s">
-        <v>504</v>
+        <v>479</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>503</v>
+        <v>480</v>
       </c>
       <c r="D109" t="s">
-        <v>504</v>
+        <v>481</v>
       </c>
       <c r="E109" t="s">
-        <v>510</v>
+        <v>482</v>
       </c>
       <c r="F109" t="s">
-        <v>504</v>
+        <v>483</v>
       </c>
       <c r="G109" t="s">
-        <v>507</v>
+        <v>484</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>503</v>
+        <v>480</v>
       </c>
       <c r="I109">
         <v>2</v>
       </c>
       <c r="J109" t="s">
-        <v>504</v>
+        <v>481</v>
       </c>
       <c r="K109" s="9" t="s">
-        <v>508</v>
+        <v>473</v>
       </c>
       <c r="L109" t="s">
         <v>20</v>
       </c>
       <c r="M109" t="s">
-        <v>504</v>
+        <v>474</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
-        <v>509</v>
+        <v>485</v>
       </c>
       <c r="B110" t="s">
-        <v>511</v>
+        <v>486</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>503</v>
+        <v>487</v>
       </c>
       <c r="D110" t="s">
-        <v>504</v>
+        <v>488</v>
+      </c>
+      <c r="E110" t="s">
+        <v>489</v>
+      </c>
+      <c r="F110" t="s">
+        <v>490</v>
       </c>
       <c r="G110" t="s">
-        <v>507</v>
+        <v>491</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>503</v>
+        <v>487</v>
       </c>
       <c r="I110">
         <v>2</v>
       </c>
       <c r="J110" t="s">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="K110" s="9" t="s">
-        <v>508</v>
+        <v>473</v>
       </c>
       <c r="L110" t="s">
         <v>20</v>
       </c>
       <c r="M110" t="s">
-        <v>504</v>
+        <v>474</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>512</v>
+        <v>492</v>
       </c>
       <c r="B111" t="s">
-        <v>513</v>
+        <v>493</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>514</v>
+        <v>494</v>
       </c>
       <c r="D111" t="s">
-        <v>515</v>
+        <v>493</v>
       </c>
       <c r="G111" t="s">
-        <v>516</v>
+        <v>495</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>514</v>
+        <v>494</v>
       </c>
       <c r="I111">
         <v>2</v>
       </c>
       <c r="J111" t="s">
-        <v>517</v>
+        <v>493</v>
       </c>
       <c r="K111" s="9" t="s">
-        <v>518</v>
+        <v>496</v>
       </c>
       <c r="L111" t="s">
         <v>20</v>
       </c>
       <c r="M111" t="s">
-        <v>519</v>
+        <v>497</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
-        <v>520</v>
+        <v>498</v>
       </c>
       <c r="B112" t="s">
-        <v>521</v>
+        <v>499</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>522</v>
+        <v>500</v>
       </c>
       <c r="D112" t="s">
-        <v>521</v>
+        <v>501</v>
+      </c>
+      <c r="E112" t="s">
+        <v>502</v>
+      </c>
+      <c r="F112" t="s">
+        <v>503</v>
       </c>
       <c r="G112" t="s">
-        <v>523</v>
+        <v>504</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>522</v>
+        <v>500</v>
       </c>
       <c r="I112">
         <v>2</v>
       </c>
       <c r="J112" t="s">
-        <v>521</v>
+        <v>501</v>
       </c>
       <c r="K112" s="9" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="L112" t="s">
         <v>20</v>
       </c>
       <c r="M112" t="s">
-        <v>519</v>
+        <v>501</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="B113" t="s">
-        <v>524</v>
+        <v>501</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="D113" t="s">
-        <v>526</v>
+        <v>501</v>
       </c>
       <c r="E113" t="s">
-        <v>527</v>
+        <v>507</v>
       </c>
       <c r="F113" t="s">
-        <v>528</v>
+        <v>501</v>
       </c>
       <c r="G113" t="s">
-        <v>529</v>
+        <v>504</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="I113">
         <v>2</v>
       </c>
       <c r="J113" t="s">
-        <v>526</v>
+        <v>501</v>
       </c>
       <c r="K113" s="9" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="L113" t="s">
         <v>20</v>
       </c>
       <c r="M113" t="s">
-        <v>519</v>
+        <v>501</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
-        <v>530</v>
+        <v>506</v>
       </c>
       <c r="B114" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>532</v>
+        <v>500</v>
       </c>
       <c r="D114" t="s">
-        <v>533</v>
+        <v>501</v>
       </c>
       <c r="G114" t="s">
-        <v>534</v>
+        <v>504</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>532</v>
+        <v>500</v>
       </c>
       <c r="I114">
         <v>2</v>
       </c>
       <c r="J114" t="s">
-        <v>533</v>
+        <v>501</v>
       </c>
       <c r="K114" s="9" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="L114" t="s">
         <v>20</v>
       </c>
       <c r="M114" t="s">
-        <v>519</v>
+        <v>501</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>535</v>
+        <v>509</v>
       </c>
       <c r="B115" t="s">
-        <v>536</v>
+        <v>510</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>525</v>
+        <v>511</v>
       </c>
       <c r="D115" t="s">
-        <v>526</v>
-      </c>
-      <c r="E115" t="s">
-        <v>537</v>
-      </c>
-      <c r="F115" t="s">
-        <v>536</v>
+        <v>512</v>
       </c>
       <c r="G115" t="s">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>525</v>
+        <v>511</v>
       </c>
       <c r="I115">
         <v>2</v>
       </c>
       <c r="J115" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="K115" s="9" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="L115" t="s">
         <v>20</v>
       </c>
       <c r="M115" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
-        <v>354</v>
+        <v>517</v>
       </c>
       <c r="B116" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>539</v>
+        <v>519</v>
       </c>
       <c r="D116" t="s">
-        <v>540</v>
-      </c>
-      <c r="E116" t="s">
-        <v>541</v>
-      </c>
-      <c r="F116" t="s">
-        <v>542</v>
+        <v>518</v>
       </c>
       <c r="G116" t="s">
-        <v>543</v>
+        <v>520</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>539</v>
+        <v>519</v>
       </c>
       <c r="I116">
         <v>2</v>
       </c>
       <c r="J116" t="s">
-        <v>540</v>
+        <v>518</v>
       </c>
       <c r="K116" s="9" t="s">
-        <v>544</v>
+        <v>515</v>
       </c>
       <c r="L116" t="s">
         <v>20</v>
       </c>
       <c r="M116" t="s">
-        <v>545</v>
+        <v>516</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>546</v>
+        <v>509</v>
       </c>
       <c r="B117" t="s">
-        <v>547</v>
+        <v>521</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>548</v>
+        <v>522</v>
       </c>
       <c r="D117" t="s">
-        <v>549</v>
+        <v>523</v>
+      </c>
+      <c r="E117" t="s">
+        <v>524</v>
+      </c>
+      <c r="F117" t="s">
+        <v>525</v>
       </c>
       <c r="G117" t="s">
-        <v>550</v>
+        <v>526</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>548</v>
+        <v>522</v>
       </c>
       <c r="I117">
         <v>2</v>
       </c>
       <c r="J117" t="s">
-        <v>549</v>
+        <v>523</v>
       </c>
       <c r="K117" s="9" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="L117" t="s">
         <v>20</v>
       </c>
       <c r="M117" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
-        <v>512</v>
+        <v>527</v>
       </c>
       <c r="B118" t="s">
-        <v>551</v>
+        <v>528</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="D118" t="s">
-        <v>526</v>
-      </c>
-      <c r="E118" t="s">
-        <v>552</v>
-      </c>
-      <c r="F118" t="s">
-        <v>553</v>
+        <v>530</v>
       </c>
       <c r="G118" t="s">
+        <v>531</v>
+      </c>
+      <c r="H118" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="H118" s="3" t="s">
-        <v>525</v>
-      </c>
       <c r="I118">
         <v>2</v>
       </c>
       <c r="J118" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="K118" s="9" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="L118" t="s">
         <v>20</v>
       </c>
       <c r="M118" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>512</v>
+        <v>532</v>
       </c>
       <c r="B119" t="s">
-        <v>554</v>
+        <v>533</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>555</v>
+        <v>522</v>
       </c>
       <c r="D119" t="s">
-        <v>554</v>
+        <v>523</v>
+      </c>
+      <c r="E119" t="s">
+        <v>534</v>
+      </c>
+      <c r="F119" t="s">
+        <v>533</v>
       </c>
       <c r="G119" t="s">
-        <v>556</v>
+        <v>526</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>555</v>
+        <v>522</v>
       </c>
       <c r="I119">
         <v>2</v>
       </c>
       <c r="J119" t="s">
-        <v>554</v>
+        <v>523</v>
       </c>
       <c r="K119" s="9" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="L119" t="s">
         <v>20</v>
       </c>
       <c r="M119" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
-        <v>557</v>
+        <v>352</v>
       </c>
       <c r="B120" t="s">
-        <v>558</v>
+        <v>535</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="D120" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="E120" t="s">
-        <v>559</v>
+        <v>538</v>
       </c>
       <c r="F120" t="s">
-        <v>560</v>
+        <v>539</v>
       </c>
       <c r="G120" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="I120">
         <v>2</v>
       </c>
       <c r="J120" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="K120" s="9" t="s">
-        <v>518</v>
+        <v>541</v>
       </c>
       <c r="L120" t="s">
         <v>20</v>
       </c>
       <c r="M120" t="s">
-        <v>519</v>
+        <v>542</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>561</v>
+        <v>543</v>
       </c>
       <c r="B121" t="s">
-        <v>562</v>
+        <v>544</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
       <c r="D121" t="s">
-        <v>562</v>
+        <v>546</v>
       </c>
       <c r="G121" t="s">
-        <v>564</v>
+        <v>547</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
       <c r="I121">
         <v>2</v>
       </c>
       <c r="J121" t="s">
-        <v>562</v>
+        <v>546</v>
       </c>
       <c r="K121" s="9" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="L121" t="s">
         <v>20</v>
       </c>
       <c r="M121" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B122" t="s">
-        <v>877</v>
+        <v>548</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D122" t="s">
-        <v>879</v>
+        <v>523</v>
+      </c>
+      <c r="E122" t="s">
+        <v>549</v>
+      </c>
+      <c r="F122" t="s">
+        <v>550</v>
       </c>
       <c r="G122" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="I122">
         <v>2</v>
       </c>
       <c r="J122" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="K122" s="9" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="L122" t="s">
         <v>20</v>
       </c>
       <c r="M122" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B123" t="s">
-        <v>878</v>
+        <v>551</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>881</v>
+        <v>552</v>
       </c>
       <c r="D123" t="s">
-        <v>883</v>
+        <v>551</v>
       </c>
       <c r="G123" t="s">
-        <v>880</v>
+        <v>553</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>881</v>
+        <v>552</v>
       </c>
       <c r="I123">
         <v>2</v>
       </c>
       <c r="J123" t="s">
-        <v>882</v>
+        <v>551</v>
       </c>
       <c r="K123" s="9" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="L123" t="s">
         <v>20</v>
       </c>
       <c r="M123" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
-        <v>512</v>
+        <v>554</v>
       </c>
       <c r="B124" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>566</v>
+        <v>522</v>
       </c>
       <c r="D124" t="s">
-        <v>565</v>
+        <v>523</v>
+      </c>
+      <c r="E124" t="s">
+        <v>556</v>
+      </c>
+      <c r="F124" t="s">
+        <v>557</v>
       </c>
       <c r="G124" t="s">
-        <v>567</v>
+        <v>526</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>566</v>
+        <v>522</v>
       </c>
       <c r="I124">
         <v>2</v>
       </c>
       <c r="J124" t="s">
-        <v>565</v>
+        <v>523</v>
       </c>
       <c r="K124" s="9" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="L124" t="s">
         <v>20</v>
       </c>
       <c r="M124" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="B125" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="D125" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="G125" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="I125">
         <v>2</v>
       </c>
       <c r="J125" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="K125" s="9" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="L125" t="s">
         <v>20</v>
       </c>
       <c r="M125" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
-        <v>572</v>
+        <v>509</v>
       </c>
       <c r="B126" t="s">
-        <v>573</v>
+        <v>874</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>574</v>
+        <v>522</v>
       </c>
       <c r="D126" t="s">
-        <v>575</v>
+        <v>876</v>
       </c>
       <c r="G126" t="s">
-        <v>576</v>
+        <v>526</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>574</v>
+        <v>522</v>
       </c>
       <c r="I126">
         <v>2</v>
       </c>
       <c r="J126" t="s">
-        <v>575</v>
+        <v>523</v>
       </c>
       <c r="K126" s="9" t="s">
-        <v>577</v>
+        <v>515</v>
       </c>
       <c r="L126" t="s">
         <v>20</v>
       </c>
       <c r="M126" t="s">
-        <v>578</v>
+        <v>516</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>579</v>
+        <v>509</v>
       </c>
       <c r="B127" t="s">
-        <v>580</v>
+        <v>875</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>581</v>
+        <v>878</v>
       </c>
       <c r="D127" t="s">
-        <v>582</v>
+        <v>880</v>
       </c>
       <c r="G127" t="s">
-        <v>583</v>
+        <v>877</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>581</v>
+        <v>878</v>
       </c>
       <c r="I127">
         <v>2</v>
       </c>
       <c r="J127" t="s">
-        <v>582</v>
+        <v>879</v>
       </c>
       <c r="K127" s="9" t="s">
-        <v>68</v>
+        <v>515</v>
       </c>
       <c r="L127" t="s">
         <v>20</v>
       </c>
       <c r="M127" t="s">
-        <v>69</v>
+        <v>516</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B128" t="s">
+        <v>562</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="D128" t="s">
+        <v>562</v>
+      </c>
+      <c r="G128" t="s">
+        <v>564</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="I128">
+        <v>2</v>
+      </c>
+      <c r="J128" t="s">
+        <v>562</v>
+      </c>
+      <c r="K128" s="9" t="s">
         <v>515</v>
       </c>
-      <c r="C128" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="D128" t="s">
-        <v>515</v>
-      </c>
-      <c r="G128" t="s">
+      <c r="L128" t="s">
+        <v>20</v>
+      </c>
+      <c r="M128" t="s">
         <v>516</v>
-      </c>
-      <c r="H128" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="I128">
-        <v>2</v>
-      </c>
-      <c r="J128" t="s">
-        <v>517</v>
-      </c>
-      <c r="K128" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="L128" t="s">
-        <v>20</v>
-      </c>
-      <c r="M128" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>354</v>
+        <v>565</v>
       </c>
       <c r="B129" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>539</v>
+        <v>567</v>
       </c>
       <c r="D129" t="s">
-        <v>540</v>
+        <v>566</v>
       </c>
       <c r="G129" t="s">
-        <v>543</v>
+        <v>568</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>539</v>
+        <v>567</v>
       </c>
       <c r="I129">
         <v>2</v>
       </c>
       <c r="J129" t="s">
-        <v>540</v>
+        <v>566</v>
       </c>
       <c r="K129" s="9" t="s">
-        <v>544</v>
+        <v>515</v>
       </c>
       <c r="L129" t="s">
         <v>20</v>
       </c>
       <c r="M129" t="s">
-        <v>545</v>
+        <v>516</v>
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="B130" t="s">
-        <v>584</v>
+        <v>570</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>585</v>
+        <v>571</v>
       </c>
       <c r="D130" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="G130" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>585</v>
+        <v>571</v>
       </c>
       <c r="I130">
         <v>2</v>
       </c>
       <c r="J130" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="K130" s="9" t="s">
-        <v>518</v>
+        <v>574</v>
       </c>
       <c r="L130" t="s">
         <v>20</v>
       </c>
       <c r="M130" t="s">
-        <v>519</v>
+        <v>575</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>587</v>
+        <v>576</v>
       </c>
       <c r="B131" t="s">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>525</v>
+        <v>578</v>
       </c>
       <c r="D131" t="s">
-        <v>526</v>
-      </c>
-      <c r="E131" t="s">
-        <v>589</v>
-      </c>
-      <c r="F131" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="G131" t="s">
-        <v>529</v>
+        <v>580</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>525</v>
+        <v>578</v>
       </c>
       <c r="I131">
         <v>2</v>
       </c>
       <c r="J131" t="s">
-        <v>526</v>
+        <v>579</v>
       </c>
       <c r="K131" s="9" t="s">
-        <v>518</v>
+        <v>67</v>
       </c>
       <c r="L131" t="s">
         <v>20</v>
       </c>
       <c r="M131" t="s">
-        <v>519</v>
+        <v>68</v>
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" s="7" t="s">
-        <v>591</v>
+        <v>509</v>
       </c>
       <c r="B132" t="s">
-        <v>592</v>
+        <v>512</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>593</v>
+        <v>511</v>
       </c>
       <c r="D132" t="s">
-        <v>594</v>
-      </c>
-      <c r="E132" t="s">
-        <v>595</v>
-      </c>
-      <c r="F132" t="s">
-        <v>596</v>
+        <v>512</v>
       </c>
       <c r="G132" t="s">
-        <v>597</v>
+        <v>513</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>593</v>
+        <v>511</v>
       </c>
       <c r="I132">
         <v>2</v>
       </c>
       <c r="J132" t="s">
-        <v>594</v>
+        <v>514</v>
       </c>
       <c r="K132" s="9" t="s">
-        <v>598</v>
+        <v>515</v>
       </c>
       <c r="L132" t="s">
         <v>20</v>
       </c>
       <c r="M132" t="s">
-        <v>599</v>
+        <v>516</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>591</v>
+        <v>352</v>
       </c>
       <c r="B133" t="s">
-        <v>600</v>
+        <v>542</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>593</v>
+        <v>536</v>
       </c>
       <c r="D133" t="s">
-        <v>594</v>
+        <v>537</v>
       </c>
       <c r="G133" t="s">
-        <v>597</v>
+        <v>540</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>593</v>
+        <v>536</v>
       </c>
       <c r="I133">
         <v>2</v>
       </c>
       <c r="J133" t="s">
-        <v>594</v>
+        <v>537</v>
       </c>
       <c r="K133" s="9" t="s">
-        <v>598</v>
+        <v>541</v>
       </c>
       <c r="L133" t="s">
         <v>20</v>
       </c>
       <c r="M133" t="s">
-        <v>599</v>
+        <v>542</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" s="7" t="s">
-        <v>601</v>
+        <v>554</v>
       </c>
       <c r="B134" t="s">
-        <v>602</v>
+        <v>581</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>603</v>
+        <v>582</v>
       </c>
       <c r="D134" t="s">
-        <v>604</v>
+        <v>581</v>
+      </c>
+      <c r="G134" t="s">
+        <v>583</v>
+      </c>
+      <c r="H134" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="I134">
+        <v>2</v>
+      </c>
+      <c r="J134" t="s">
+        <v>581</v>
+      </c>
+      <c r="K134" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="L134" t="s">
+        <v>20</v>
+      </c>
+      <c r="M134" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>605</v>
+        <v>584</v>
       </c>
       <c r="B135" t="s">
-        <v>892</v>
+        <v>585</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>606</v>
+        <v>522</v>
       </c>
       <c r="D135" t="s">
-        <v>608</v>
+        <v>523</v>
+      </c>
+      <c r="E135" t="s">
+        <v>586</v>
+      </c>
+      <c r="F135" t="s">
+        <v>587</v>
       </c>
       <c r="G135" t="s">
-        <v>607</v>
+        <v>526</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>606</v>
+        <v>522</v>
       </c>
       <c r="I135">
         <v>2</v>
       </c>
       <c r="J135" t="s">
-        <v>608</v>
+        <v>523</v>
       </c>
       <c r="K135" s="9" t="s">
-        <v>609</v>
+        <v>515</v>
       </c>
       <c r="L135" t="s">
         <v>20</v>
       </c>
       <c r="M135" t="s">
-        <v>610</v>
+        <v>516</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" s="7" t="s">
-        <v>893</v>
+        <v>588</v>
       </c>
       <c r="B136" t="s">
-        <v>899</v>
+        <v>589</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>884</v>
+        <v>590</v>
       </c>
       <c r="D136" t="s">
-        <v>888</v>
+        <v>591</v>
+      </c>
+      <c r="E136" t="s">
+        <v>592</v>
+      </c>
+      <c r="F136" t="s">
+        <v>593</v>
       </c>
       <c r="G136" t="s">
-        <v>901</v>
+        <v>594</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>884</v>
+        <v>590</v>
       </c>
       <c r="I136">
         <v>2</v>
       </c>
       <c r="J136" t="s">
-        <v>888</v>
+        <v>591</v>
       </c>
       <c r="K136" s="9" t="s">
-        <v>902</v>
+        <v>595</v>
       </c>
       <c r="L136" t="s">
         <v>20</v>
       </c>
       <c r="M136" t="s">
-        <v>888</v>
+        <v>596</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>894</v>
+        <v>588</v>
       </c>
       <c r="B137" t="s">
-        <v>900</v>
+        <v>597</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>885</v>
+        <v>590</v>
       </c>
       <c r="D137" t="s">
-        <v>889</v>
+        <v>591</v>
       </c>
       <c r="G137" t="s">
-        <v>903</v>
+        <v>594</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>885</v>
+        <v>590</v>
       </c>
       <c r="I137">
         <v>2</v>
       </c>
       <c r="J137" t="s">
-        <v>889</v>
+        <v>591</v>
       </c>
       <c r="K137" s="9" t="s">
-        <v>904</v>
+        <v>595</v>
       </c>
       <c r="L137" t="s">
         <v>20</v>
       </c>
       <c r="M137" t="s">
-        <v>905</v>
+        <v>596</v>
       </c>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" s="7" t="s">
-        <v>895</v>
+        <v>598</v>
       </c>
       <c r="B138" t="s">
-        <v>898</v>
+        <v>599</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>886</v>
+        <v>600</v>
       </c>
       <c r="D138" t="s">
-        <v>890</v>
-      </c>
-      <c r="G138" t="s">
-        <v>906</v>
-      </c>
-      <c r="H138" s="3" t="s">
-        <v>886</v>
-      </c>
-      <c r="I138">
-        <v>2</v>
-      </c>
-      <c r="J138" t="s">
-        <v>890</v>
-      </c>
-      <c r="K138" s="9" t="s">
-        <v>907</v>
-      </c>
-      <c r="L138" t="s">
-        <v>20</v>
-      </c>
-      <c r="M138" t="s">
-        <v>890</v>
+        <v>601</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>896</v>
+        <v>602</v>
       </c>
       <c r="B139" t="s">
-        <v>897</v>
+        <v>889</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>887</v>
+        <v>603</v>
       </c>
       <c r="D139" t="s">
-        <v>891</v>
+        <v>605</v>
       </c>
       <c r="G139" t="s">
-        <v>908</v>
+        <v>604</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>887</v>
+        <v>603</v>
       </c>
       <c r="I139">
         <v>2</v>
       </c>
       <c r="J139" t="s">
-        <v>891</v>
+        <v>605</v>
       </c>
       <c r="K139" s="9" t="s">
-        <v>909</v>
+        <v>606</v>
       </c>
       <c r="L139" t="s">
         <v>20</v>
       </c>
       <c r="M139" t="s">
-        <v>891</v>
+        <v>607</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" s="7" t="s">
-        <v>611</v>
+        <v>890</v>
       </c>
       <c r="B140" t="s">
-        <v>612</v>
+        <v>896</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>613</v>
+        <v>881</v>
       </c>
       <c r="D140" t="s">
-        <v>614</v>
+        <v>885</v>
       </c>
       <c r="G140" t="s">
-        <v>615</v>
+        <v>898</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>613</v>
+        <v>881</v>
       </c>
       <c r="I140">
         <v>2</v>
       </c>
       <c r="J140" t="s">
-        <v>614</v>
+        <v>885</v>
       </c>
       <c r="K140" s="9" t="s">
-        <v>616</v>
+        <v>899</v>
       </c>
       <c r="L140" t="s">
         <v>20</v>
       </c>
       <c r="M140" t="s">
-        <v>614</v>
+        <v>885</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>617</v>
+        <v>891</v>
       </c>
       <c r="B141" t="s">
-        <v>618</v>
+        <v>897</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>619</v>
+        <v>882</v>
       </c>
       <c r="D141" t="s">
-        <v>620</v>
-      </c>
-      <c r="E141" t="s">
-        <v>621</v>
-      </c>
-      <c r="F141" t="s">
-        <v>618</v>
+        <v>886</v>
       </c>
       <c r="G141" t="s">
-        <v>622</v>
+        <v>900</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>619</v>
+        <v>882</v>
       </c>
       <c r="I141">
         <v>2</v>
       </c>
       <c r="J141" t="s">
-        <v>620</v>
+        <v>886</v>
       </c>
       <c r="K141" s="9" t="s">
-        <v>623</v>
+        <v>901</v>
       </c>
       <c r="L141" t="s">
         <v>20</v>
       </c>
       <c r="M141" t="s">
-        <v>624</v>
+        <v>902</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" s="7" t="s">
-        <v>625</v>
+        <v>892</v>
       </c>
       <c r="B142" t="s">
-        <v>626</v>
+        <v>895</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>619</v>
+        <v>883</v>
       </c>
       <c r="D142" t="s">
-        <v>620</v>
+        <v>887</v>
       </c>
       <c r="G142" t="s">
-        <v>622</v>
+        <v>903</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>619</v>
+        <v>883</v>
       </c>
       <c r="I142">
         <v>2</v>
       </c>
       <c r="J142" t="s">
-        <v>620</v>
+        <v>887</v>
       </c>
       <c r="K142" s="9" t="s">
-        <v>623</v>
+        <v>904</v>
       </c>
       <c r="L142" t="s">
         <v>20</v>
       </c>
       <c r="M142" t="s">
-        <v>624</v>
+        <v>887</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>625</v>
+        <v>893</v>
       </c>
       <c r="B143" t="s">
-        <v>627</v>
+        <v>894</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>619</v>
+        <v>884</v>
       </c>
       <c r="D143" t="s">
-        <v>620</v>
+        <v>888</v>
       </c>
       <c r="G143" t="s">
-        <v>622</v>
+        <v>905</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>619</v>
+        <v>884</v>
       </c>
       <c r="I143">
         <v>2</v>
       </c>
       <c r="J143" t="s">
-        <v>620</v>
+        <v>888</v>
       </c>
       <c r="K143" s="9" t="s">
-        <v>623</v>
+        <v>906</v>
       </c>
       <c r="L143" t="s">
         <v>20</v>
       </c>
       <c r="M143" t="s">
-        <v>624</v>
+        <v>888</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" s="7" t="s">
-        <v>628</v>
+        <v>608</v>
       </c>
       <c r="B144" t="s">
-        <v>629</v>
+        <v>609</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>630</v>
+        <v>610</v>
       </c>
       <c r="D144" t="s">
-        <v>631</v>
+        <v>611</v>
       </c>
       <c r="G144" t="s">
-        <v>632</v>
+        <v>612</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>630</v>
+        <v>610</v>
       </c>
       <c r="I144">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J144" t="s">
-        <v>631</v>
+        <v>611</v>
       </c>
       <c r="K144" s="9" t="s">
-        <v>633</v>
+        <v>613</v>
       </c>
       <c r="L144" t="s">
-        <v>634</v>
+        <v>20</v>
       </c>
       <c r="M144" t="s">
-        <v>635</v>
+        <v>611</v>
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>628</v>
+        <v>614</v>
       </c>
       <c r="B145" t="s">
-        <v>636</v>
+        <v>615</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>637</v>
+        <v>616</v>
       </c>
       <c r="D145" t="s">
-        <v>639</v>
+        <v>617</v>
+      </c>
+      <c r="E145" t="s">
+        <v>618</v>
+      </c>
+      <c r="F145" t="s">
+        <v>615</v>
       </c>
       <c r="G145" t="s">
-        <v>638</v>
+        <v>619</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>637</v>
+        <v>616</v>
       </c>
       <c r="I145">
         <v>2</v>
       </c>
       <c r="J145" t="s">
-        <v>639</v>
+        <v>617</v>
       </c>
       <c r="K145" s="9" t="s">
-        <v>598</v>
+        <v>620</v>
       </c>
       <c r="L145" t="s">
         <v>20</v>
       </c>
       <c r="M145" t="s">
-        <v>599</v>
+        <v>621</v>
       </c>
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146" s="7" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="B146" t="s">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>910</v>
+        <v>616</v>
       </c>
       <c r="D146" t="s">
-        <v>911</v>
+        <v>617</v>
       </c>
       <c r="G146" t="s">
-        <v>912</v>
+        <v>619</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>910</v>
+        <v>616</v>
       </c>
       <c r="I146">
         <v>2</v>
       </c>
       <c r="J146" t="s">
-        <v>911</v>
+        <v>617</v>
       </c>
       <c r="K146" s="9" t="s">
-        <v>598</v>
+        <v>620</v>
       </c>
       <c r="L146" t="s">
         <v>20</v>
       </c>
       <c r="M146" t="s">
-        <v>599</v>
+        <v>621</v>
       </c>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>640</v>
+        <v>622</v>
       </c>
       <c r="B147" t="s">
-        <v>641</v>
+        <v>624</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>642</v>
+        <v>616</v>
       </c>
       <c r="D147" t="s">
-        <v>641</v>
+        <v>617</v>
       </c>
       <c r="G147" t="s">
-        <v>643</v>
+        <v>619</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>642</v>
+        <v>616</v>
       </c>
       <c r="I147">
         <v>2</v>
       </c>
       <c r="J147" t="s">
-        <v>641</v>
+        <v>617</v>
       </c>
       <c r="K147" s="9" t="s">
-        <v>644</v>
+        <v>620</v>
       </c>
       <c r="L147" t="s">
         <v>20</v>
       </c>
       <c r="M147" t="s">
-        <v>645</v>
+        <v>621</v>
       </c>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" s="7" t="s">
-        <v>640</v>
+        <v>625</v>
       </c>
       <c r="B148" t="s">
-        <v>646</v>
+        <v>626</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>647</v>
+        <v>627</v>
       </c>
       <c r="D148" t="s">
-        <v>646</v>
+        <v>628</v>
       </c>
       <c r="G148" t="s">
-        <v>648</v>
+        <v>629</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>647</v>
+        <v>627</v>
       </c>
       <c r="I148">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J148" t="s">
-        <v>646</v>
+        <v>628</v>
       </c>
       <c r="K148" s="9" t="s">
-        <v>644</v>
+        <v>630</v>
       </c>
       <c r="L148" t="s">
-        <v>20</v>
+        <v>631</v>
       </c>
       <c r="M148" t="s">
-        <v>645</v>
+        <v>632</v>
       </c>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>640</v>
+        <v>625</v>
       </c>
       <c r="B149" t="s">
-        <v>649</v>
+        <v>633</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>650</v>
+        <v>634</v>
       </c>
       <c r="D149" t="s">
-        <v>649</v>
+        <v>636</v>
       </c>
       <c r="G149" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>650</v>
+        <v>634</v>
       </c>
       <c r="I149">
         <v>2</v>
       </c>
       <c r="J149" t="s">
-        <v>649</v>
+        <v>636</v>
       </c>
       <c r="K149" s="9" t="s">
-        <v>644</v>
+        <v>595</v>
       </c>
       <c r="L149" t="s">
         <v>20</v>
       </c>
       <c r="M149" t="s">
-        <v>645</v>
+        <v>596</v>
       </c>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" s="7" t="s">
-        <v>652</v>
+        <v>625</v>
       </c>
       <c r="B150" t="s">
-        <v>653</v>
+        <v>633</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>654</v>
+        <v>907</v>
       </c>
       <c r="D150" t="s">
-        <v>655</v>
-      </c>
-      <c r="E150" t="s">
-        <v>656</v>
-      </c>
-      <c r="F150" t="s">
-        <v>657</v>
+        <v>908</v>
       </c>
       <c r="G150" t="s">
-        <v>658</v>
+        <v>909</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>654</v>
+        <v>907</v>
       </c>
       <c r="I150">
         <v>2</v>
       </c>
       <c r="J150" t="s">
-        <v>655</v>
+        <v>908</v>
       </c>
       <c r="K150" s="9" t="s">
-        <v>659</v>
+        <v>595</v>
       </c>
       <c r="L150" t="s">
         <v>20</v>
       </c>
       <c r="M150" t="s">
-        <v>655</v>
+        <v>596</v>
       </c>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>660</v>
+        <v>637</v>
       </c>
       <c r="B151" t="s">
-        <v>661</v>
+        <v>638</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>662</v>
+        <v>639</v>
       </c>
       <c r="D151" t="s">
-        <v>661</v>
+        <v>638</v>
       </c>
       <c r="G151" t="s">
-        <v>663</v>
+        <v>640</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>662</v>
+        <v>639</v>
       </c>
       <c r="I151">
         <v>2</v>
       </c>
       <c r="J151" t="s">
-        <v>661</v>
+        <v>638</v>
       </c>
       <c r="K151" s="9" t="s">
-        <v>664</v>
+        <v>641</v>
       </c>
       <c r="L151" t="s">
         <v>20</v>
       </c>
       <c r="M151" t="s">
-        <v>665</v>
+        <v>642</v>
       </c>
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
-        <v>660</v>
+        <v>637</v>
       </c>
       <c r="B152" t="s">
-        <v>666</v>
+        <v>643</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>667</v>
+        <v>644</v>
       </c>
       <c r="D152" t="s">
-        <v>668</v>
+        <v>643</v>
       </c>
       <c r="G152" t="s">
-        <v>669</v>
+        <v>645</v>
       </c>
       <c r="H152" s="3" t="s">
-        <v>667</v>
+        <v>644</v>
       </c>
       <c r="I152">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J152" t="s">
-        <v>668</v>
+        <v>643</v>
       </c>
       <c r="K152" s="9" t="s">
-        <v>670</v>
+        <v>641</v>
       </c>
       <c r="L152" t="s">
-        <v>671</v>
+        <v>20</v>
       </c>
       <c r="M152" t="s">
-        <v>672</v>
+        <v>642</v>
       </c>
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>673</v>
+        <v>637</v>
       </c>
       <c r="B153" t="s">
-        <v>674</v>
+        <v>646</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>675</v>
+        <v>647</v>
       </c>
       <c r="D153" t="s">
-        <v>676</v>
-      </c>
-      <c r="E153" t="s">
-        <v>677</v>
-      </c>
-      <c r="F153" t="s">
-        <v>678</v>
+        <v>646</v>
       </c>
       <c r="G153" t="s">
-        <v>679</v>
+        <v>648</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>675</v>
+        <v>647</v>
       </c>
       <c r="I153">
         <v>2</v>
       </c>
       <c r="J153" t="s">
-        <v>676</v>
+        <v>646</v>
       </c>
       <c r="K153" s="9" t="s">
-        <v>68</v>
+        <v>641</v>
       </c>
       <c r="L153" t="s">
         <v>20</v>
       </c>
       <c r="M153" t="s">
-        <v>69</v>
+        <v>642</v>
       </c>
     </row>
     <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
-        <v>680</v>
+        <v>649</v>
       </c>
       <c r="B154" t="s">
-        <v>681</v>
+        <v>650</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>682</v>
+        <v>651</v>
       </c>
       <c r="D154" t="s">
-        <v>681</v>
+        <v>652</v>
+      </c>
+      <c r="E154" t="s">
+        <v>653</v>
+      </c>
+      <c r="F154" t="s">
+        <v>654</v>
       </c>
       <c r="G154" t="s">
-        <v>683</v>
+        <v>655</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>682</v>
+        <v>651</v>
       </c>
       <c r="I154">
         <v>2</v>
       </c>
       <c r="J154" t="s">
-        <v>681</v>
+        <v>652</v>
       </c>
       <c r="K154" s="9" t="s">
-        <v>684</v>
+        <v>656</v>
       </c>
       <c r="L154" t="s">
         <v>20</v>
       </c>
       <c r="M154" t="s">
-        <v>685</v>
+        <v>652</v>
       </c>
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>686</v>
+        <v>657</v>
       </c>
       <c r="B155" t="s">
-        <v>687</v>
+        <v>658</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>688</v>
+        <v>659</v>
       </c>
       <c r="D155" t="s">
-        <v>687</v>
+        <v>658</v>
       </c>
       <c r="G155" t="s">
-        <v>689</v>
+        <v>660</v>
       </c>
       <c r="H155" s="3" t="s">
-        <v>688</v>
+        <v>659</v>
       </c>
       <c r="I155">
         <v>2</v>
       </c>
       <c r="J155" t="s">
-        <v>687</v>
+        <v>658</v>
       </c>
       <c r="K155" s="9" t="s">
-        <v>690</v>
+        <v>661</v>
       </c>
       <c r="L155" t="s">
         <v>20</v>
       </c>
       <c r="M155" t="s">
-        <v>691</v>
+        <v>662</v>
       </c>
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A156" s="7" t="s">
-        <v>686</v>
+        <v>657</v>
       </c>
       <c r="B156" t="s">
-        <v>692</v>
+        <v>663</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>693</v>
+        <v>664</v>
       </c>
       <c r="D156" t="s">
-        <v>694</v>
+        <v>665</v>
       </c>
       <c r="G156" t="s">
-        <v>695</v>
+        <v>666</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>693</v>
+        <v>664</v>
       </c>
       <c r="I156">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J156" t="s">
-        <v>694</v>
+        <v>665</v>
       </c>
       <c r="K156" s="9" t="s">
-        <v>690</v>
+        <v>667</v>
       </c>
       <c r="L156" t="s">
-        <v>20</v>
+        <v>668</v>
       </c>
       <c r="M156" t="s">
-        <v>691</v>
+        <v>669</v>
       </c>
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
       <c r="B157" t="s">
-        <v>697</v>
+        <v>671</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>698</v>
+        <v>672</v>
       </c>
       <c r="D157" t="s">
-        <v>699</v>
+        <v>673</v>
+      </c>
+      <c r="E157" t="s">
+        <v>674</v>
+      </c>
+      <c r="F157" t="s">
+        <v>675</v>
       </c>
       <c r="G157" t="s">
-        <v>700</v>
+        <v>676</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>698</v>
+        <v>672</v>
       </c>
       <c r="I157">
         <v>2</v>
       </c>
       <c r="J157" t="s">
-        <v>699</v>
+        <v>673</v>
       </c>
       <c r="K157" s="9" t="s">
-        <v>701</v>
+        <v>67</v>
       </c>
       <c r="L157" t="s">
         <v>20</v>
       </c>
       <c r="M157" t="s">
-        <v>702</v>
+        <v>68</v>
       </c>
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A158" s="7" t="s">
-        <v>703</v>
+        <v>677</v>
       </c>
       <c r="B158" t="s">
-        <v>704</v>
+        <v>678</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>705</v>
+        <v>679</v>
       </c>
       <c r="D158" t="s">
-        <v>704</v>
+        <v>678</v>
       </c>
       <c r="G158" t="s">
-        <v>706</v>
+        <v>680</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>705</v>
+        <v>679</v>
       </c>
       <c r="I158">
         <v>2</v>
       </c>
       <c r="J158" t="s">
-        <v>704</v>
+        <v>678</v>
       </c>
       <c r="K158" s="9" t="s">
-        <v>707</v>
+        <v>681</v>
       </c>
       <c r="L158" t="s">
         <v>20</v>
       </c>
       <c r="M158" t="s">
-        <v>708</v>
+        <v>682</v>
       </c>
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>709</v>
+        <v>683</v>
       </c>
       <c r="B159" t="s">
-        <v>710</v>
+        <v>684</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>711</v>
+        <v>685</v>
       </c>
       <c r="D159" t="s">
-        <v>712</v>
+        <v>684</v>
       </c>
       <c r="G159" t="s">
-        <v>713</v>
+        <v>686</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>711</v>
+        <v>685</v>
       </c>
       <c r="I159">
         <v>2</v>
       </c>
       <c r="J159" t="s">
-        <v>712</v>
+        <v>684</v>
       </c>
       <c r="K159" s="9" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="L159" t="s">
         <v>20</v>
       </c>
       <c r="M159" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="160" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A160" s="7" t="s">
-        <v>714</v>
+        <v>683</v>
       </c>
       <c r="B160" t="s">
-        <v>715</v>
+        <v>689</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>716</v>
+        <v>690</v>
       </c>
       <c r="D160" t="s">
-        <v>717</v>
-      </c>
-      <c r="E160" t="s">
-        <v>718</v>
-      </c>
-      <c r="F160" t="s">
-        <v>719</v>
+        <v>691</v>
       </c>
       <c r="G160" t="s">
-        <v>720</v>
+        <v>692</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>716</v>
+        <v>690</v>
       </c>
       <c r="I160">
         <v>2</v>
       </c>
       <c r="J160" t="s">
-        <v>717</v>
+        <v>691</v>
       </c>
       <c r="K160" s="9" t="s">
-        <v>721</v>
+        <v>687</v>
       </c>
       <c r="L160" t="s">
         <v>20</v>
       </c>
       <c r="M160" t="s">
-        <v>722</v>
+        <v>688</v>
       </c>
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>723</v>
+        <v>693</v>
       </c>
       <c r="B161" t="s">
-        <v>724</v>
+        <v>694</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>716</v>
+        <v>695</v>
       </c>
       <c r="D161" t="s">
-        <v>717</v>
-      </c>
-      <c r="E161" t="s">
-        <v>725</v>
-      </c>
-      <c r="F161" t="s">
-        <v>726</v>
+        <v>696</v>
       </c>
       <c r="G161" t="s">
-        <v>720</v>
+        <v>697</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>716</v>
+        <v>695</v>
       </c>
       <c r="I161">
         <v>2</v>
       </c>
       <c r="J161" t="s">
-        <v>717</v>
+        <v>696</v>
       </c>
       <c r="K161" s="9" t="s">
-        <v>721</v>
+        <v>698</v>
       </c>
       <c r="L161" t="s">
         <v>20</v>
       </c>
       <c r="M161" t="s">
-        <v>722</v>
+        <v>699</v>
       </c>
     </row>
     <row r="162" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A162" s="7" t="s">
-        <v>727</v>
+        <v>700</v>
       </c>
       <c r="B162" t="s">
-        <v>728</v>
+        <v>701</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>729</v>
+        <v>702</v>
       </c>
       <c r="D162" t="s">
-        <v>728</v>
+        <v>701</v>
       </c>
       <c r="G162" t="s">
-        <v>730</v>
+        <v>703</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>729</v>
+        <v>702</v>
       </c>
       <c r="I162">
         <v>2</v>
       </c>
       <c r="J162" t="s">
-        <v>728</v>
+        <v>701</v>
       </c>
       <c r="K162" s="9" t="s">
-        <v>731</v>
+        <v>704</v>
       </c>
       <c r="L162" t="s">
         <v>20</v>
       </c>
       <c r="M162" t="s">
-        <v>728</v>
+        <v>705</v>
       </c>
     </row>
     <row r="163" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>732</v>
+        <v>706</v>
       </c>
       <c r="B163" t="s">
-        <v>733</v>
+        <v>707</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>734</v>
+        <v>708</v>
       </c>
       <c r="D163" t="s">
-        <v>738</v>
+        <v>709</v>
       </c>
       <c r="G163" t="s">
-        <v>735</v>
+        <v>710</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>734</v>
+        <v>708</v>
       </c>
       <c r="I163">
         <v>2</v>
       </c>
       <c r="J163" t="s">
-        <v>736</v>
+        <v>709</v>
       </c>
       <c r="K163" s="9" t="s">
-        <v>721</v>
+        <v>687</v>
       </c>
       <c r="L163" t="s">
         <v>20</v>
       </c>
       <c r="M163" t="s">
-        <v>722</v>
+        <v>688</v>
       </c>
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A164" s="7" t="s">
-        <v>732</v>
+        <v>711</v>
       </c>
       <c r="B164" t="s">
-        <v>733</v>
+        <v>712</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>914</v>
+        <v>713</v>
       </c>
       <c r="D164" t="s">
-        <v>733</v>
+        <v>714</v>
+      </c>
+      <c r="E164" t="s">
+        <v>715</v>
+      </c>
+      <c r="F164" t="s">
+        <v>716</v>
       </c>
       <c r="G164" t="s">
-        <v>913</v>
+        <v>717</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>914</v>
+        <v>713</v>
       </c>
       <c r="I164">
         <v>2</v>
       </c>
       <c r="J164" t="s">
-        <v>733</v>
+        <v>714</v>
       </c>
       <c r="K164" s="9" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="L164" t="s">
         <v>20</v>
       </c>
       <c r="M164" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>732</v>
+        <v>720</v>
       </c>
       <c r="B165" t="s">
-        <v>737</v>
+        <v>721</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>734</v>
+        <v>713</v>
       </c>
       <c r="D165" t="s">
-        <v>738</v>
+        <v>714</v>
       </c>
       <c r="E165" t="s">
-        <v>739</v>
+        <v>722</v>
       </c>
       <c r="F165" t="s">
-        <v>740</v>
+        <v>723</v>
       </c>
       <c r="G165" t="s">
-        <v>735</v>
+        <v>717</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>734</v>
+        <v>713</v>
       </c>
       <c r="I165">
         <v>2</v>
       </c>
       <c r="J165" t="s">
-        <v>736</v>
+        <v>714</v>
       </c>
       <c r="K165" s="9" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="L165" t="s">
         <v>20</v>
       </c>
       <c r="M165" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
     </row>
     <row r="166" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A166" s="7" t="s">
-        <v>741</v>
+        <v>724</v>
       </c>
       <c r="B166" t="s">
-        <v>742</v>
+        <v>725</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>743</v>
+        <v>726</v>
       </c>
       <c r="D166" t="s">
-        <v>742</v>
+        <v>725</v>
       </c>
       <c r="G166" t="s">
-        <v>744</v>
+        <v>727</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>743</v>
+        <v>726</v>
       </c>
       <c r="I166">
         <v>2</v>
       </c>
       <c r="J166" t="s">
-        <v>742</v>
+        <v>725</v>
       </c>
       <c r="K166" s="9" t="s">
-        <v>745</v>
+        <v>728</v>
       </c>
       <c r="L166" t="s">
         <v>20</v>
       </c>
       <c r="M166" t="s">
-        <v>742</v>
+        <v>725</v>
       </c>
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>746</v>
+        <v>729</v>
       </c>
       <c r="B167" t="s">
-        <v>747</v>
+        <v>730</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>716</v>
+        <v>731</v>
       </c>
       <c r="D167" t="s">
-        <v>717</v>
-      </c>
-      <c r="E167" t="s">
-        <v>748</v>
-      </c>
-      <c r="F167" t="s">
-        <v>747</v>
+        <v>735</v>
       </c>
       <c r="G167" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>716</v>
+        <v>731</v>
       </c>
       <c r="I167">
         <v>2</v>
       </c>
       <c r="J167" t="s">
-        <v>717</v>
+        <v>733</v>
       </c>
       <c r="K167" s="9" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="L167" t="s">
         <v>20</v>
       </c>
       <c r="M167" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
     </row>
     <row r="168" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A168" s="7" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="B168" t="s">
-        <v>749</v>
+        <v>730</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>716</v>
+        <v>911</v>
       </c>
       <c r="D168" t="s">
-        <v>717</v>
-      </c>
-      <c r="E168" t="s">
-        <v>750</v>
-      </c>
-      <c r="F168" t="s">
-        <v>751</v>
+        <v>730</v>
       </c>
       <c r="G168" t="s">
-        <v>720</v>
+        <v>910</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>716</v>
+        <v>911</v>
       </c>
       <c r="I168">
         <v>2</v>
       </c>
       <c r="J168" t="s">
-        <v>717</v>
+        <v>730</v>
       </c>
       <c r="K168" s="9" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="L168" t="s">
         <v>20</v>
       </c>
       <c r="M168" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
     </row>
     <row r="169" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>752</v>
+        <v>729</v>
       </c>
       <c r="B169" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>754</v>
+        <v>731</v>
       </c>
       <c r="D169" t="s">
-        <v>755</v>
+        <v>735</v>
+      </c>
+      <c r="E169" t="s">
+        <v>736</v>
+      </c>
+      <c r="F169" t="s">
+        <v>737</v>
       </c>
       <c r="G169" t="s">
-        <v>756</v>
+        <v>732</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>754</v>
+        <v>731</v>
       </c>
       <c r="I169">
         <v>2</v>
       </c>
       <c r="J169" t="s">
-        <v>755</v>
+        <v>733</v>
       </c>
       <c r="K169" s="9" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="L169" t="s">
         <v>20</v>
       </c>
       <c r="M169" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A170" s="7" t="s">
-        <v>757</v>
+        <v>738</v>
       </c>
       <c r="B170" t="s">
-        <v>758</v>
+        <v>739</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>759</v>
+        <v>740</v>
       </c>
       <c r="D170" t="s">
-        <v>760</v>
-      </c>
-      <c r="E170" t="s">
-        <v>761</v>
-      </c>
-      <c r="F170" t="s">
-        <v>762</v>
+        <v>739</v>
       </c>
       <c r="G170" t="s">
-        <v>763</v>
+        <v>741</v>
       </c>
       <c r="H170" s="3" t="s">
-        <v>759</v>
+        <v>740</v>
       </c>
       <c r="I170">
         <v>2</v>
       </c>
       <c r="J170" t="s">
-        <v>760</v>
+        <v>739</v>
       </c>
       <c r="K170" s="9" t="s">
-        <v>764</v>
+        <v>742</v>
       </c>
       <c r="L170" t="s">
         <v>20</v>
       </c>
       <c r="M170" t="s">
-        <v>765</v>
+        <v>739</v>
       </c>
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>757</v>
+        <v>743</v>
       </c>
       <c r="B171" t="s">
-        <v>758</v>
+        <v>744</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>759</v>
+        <v>713</v>
       </c>
       <c r="D171" t="s">
-        <v>760</v>
+        <v>714</v>
       </c>
       <c r="E171" t="s">
-        <v>761</v>
+        <v>745</v>
       </c>
       <c r="F171" t="s">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="G171" t="s">
-        <v>763</v>
+        <v>717</v>
       </c>
       <c r="H171" s="3" t="s">
-        <v>759</v>
+        <v>713</v>
       </c>
       <c r="I171">
         <v>2</v>
       </c>
       <c r="J171" t="s">
-        <v>760</v>
+        <v>714</v>
       </c>
       <c r="K171" s="9" t="s">
-        <v>764</v>
+        <v>718</v>
       </c>
       <c r="L171" t="s">
         <v>20</v>
       </c>
       <c r="M171" t="s">
-        <v>765</v>
+        <v>719</v>
       </c>
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A172" s="7" t="s">
-        <v>766</v>
+        <v>720</v>
       </c>
       <c r="B172" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>768</v>
+        <v>713</v>
       </c>
       <c r="D172" t="s">
-        <v>767</v>
+        <v>714</v>
+      </c>
+      <c r="E172" t="s">
+        <v>747</v>
+      </c>
+      <c r="F172" t="s">
+        <v>748</v>
       </c>
       <c r="G172" t="s">
-        <v>769</v>
+        <v>717</v>
       </c>
       <c r="H172" s="3" t="s">
-        <v>768</v>
+        <v>713</v>
       </c>
       <c r="I172">
         <v>2</v>
       </c>
       <c r="J172" t="s">
-        <v>770</v>
+        <v>714</v>
       </c>
       <c r="K172" s="9" t="s">
-        <v>771</v>
+        <v>718</v>
       </c>
       <c r="L172" t="s">
         <v>20</v>
       </c>
       <c r="M172" t="s">
-        <v>772</v>
+        <v>719</v>
       </c>
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
-        <v>766</v>
+        <v>749</v>
       </c>
       <c r="B173" t="s">
-        <v>773</v>
+        <v>750</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>774</v>
+        <v>751</v>
       </c>
       <c r="D173" t="s">
-        <v>775</v>
+        <v>752</v>
       </c>
       <c r="G173" t="s">
-        <v>776</v>
+        <v>753</v>
       </c>
       <c r="H173" s="3" t="s">
-        <v>774</v>
+        <v>751</v>
       </c>
       <c r="I173">
         <v>2</v>
       </c>
       <c r="J173" t="s">
-        <v>777</v>
+        <v>752</v>
       </c>
       <c r="K173" s="9" t="s">
-        <v>778</v>
+        <v>718</v>
       </c>
       <c r="L173" t="s">
         <v>20</v>
       </c>
       <c r="M173" t="s">
-        <v>779</v>
+        <v>719</v>
       </c>
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A174" s="7" t="s">
-        <v>766</v>
+        <v>754</v>
       </c>
       <c r="B174" t="s">
-        <v>780</v>
+        <v>755</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>774</v>
+        <v>756</v>
       </c>
       <c r="D174" t="s">
-        <v>775</v>
+        <v>757</v>
+      </c>
+      <c r="E174" t="s">
+        <v>758</v>
+      </c>
+      <c r="F174" t="s">
+        <v>759</v>
       </c>
       <c r="G174" t="s">
-        <v>776</v>
+        <v>760</v>
       </c>
       <c r="H174" s="3" t="s">
-        <v>774</v>
+        <v>756</v>
       </c>
       <c r="I174">
         <v>2</v>
       </c>
       <c r="J174" t="s">
-        <v>777</v>
+        <v>757</v>
       </c>
       <c r="K174" s="9" t="s">
-        <v>778</v>
+        <v>761</v>
       </c>
       <c r="L174" t="s">
         <v>20</v>
       </c>
       <c r="M174" t="s">
-        <v>779</v>
+        <v>762</v>
       </c>
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
-        <v>781</v>
+        <v>754</v>
       </c>
       <c r="B175" t="s">
-        <v>782</v>
+        <v>755</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>783</v>
+        <v>756</v>
       </c>
       <c r="D175" t="s">
-        <v>782</v>
+        <v>757</v>
+      </c>
+      <c r="E175" t="s">
+        <v>758</v>
+      </c>
+      <c r="F175" t="s">
+        <v>759</v>
       </c>
       <c r="G175" t="s">
-        <v>784</v>
+        <v>760</v>
       </c>
       <c r="H175" s="3" t="s">
-        <v>783</v>
+        <v>756</v>
       </c>
       <c r="I175">
         <v>2</v>
       </c>
       <c r="J175" t="s">
-        <v>782</v>
+        <v>757</v>
       </c>
       <c r="K175" s="9" t="s">
-        <v>785</v>
+        <v>761</v>
       </c>
       <c r="L175" t="s">
         <v>20</v>
       </c>
       <c r="M175" t="s">
-        <v>782</v>
+        <v>762</v>
       </c>
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A176" s="7" t="s">
-        <v>786</v>
+        <v>763</v>
       </c>
       <c r="B176" t="s">
-        <v>787</v>
+        <v>764</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>788</v>
+        <v>765</v>
       </c>
       <c r="D176" t="s">
-        <v>789</v>
-      </c>
-      <c r="E176" t="s">
-        <v>790</v>
-      </c>
-      <c r="F176" t="s">
-        <v>787</v>
+        <v>764</v>
       </c>
       <c r="G176" t="s">
-        <v>791</v>
+        <v>766</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>788</v>
+        <v>765</v>
       </c>
       <c r="I176">
         <v>2</v>
       </c>
       <c r="J176" t="s">
-        <v>789</v>
+        <v>767</v>
       </c>
       <c r="K176" s="9" t="s">
-        <v>792</v>
+        <v>768</v>
       </c>
       <c r="L176" t="s">
         <v>20</v>
       </c>
       <c r="M176" t="s">
-        <v>789</v>
+        <v>769</v>
       </c>
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
-        <v>793</v>
+        <v>763</v>
       </c>
       <c r="B177" t="s">
-        <v>794</v>
+        <v>770</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>795</v>
+        <v>771</v>
       </c>
       <c r="D177" t="s">
-        <v>796</v>
-      </c>
-      <c r="E177" t="s">
-        <v>797</v>
-      </c>
-      <c r="F177" t="s">
-        <v>798</v>
+        <v>772</v>
       </c>
       <c r="G177" t="s">
-        <v>799</v>
+        <v>773</v>
       </c>
       <c r="H177" s="3" t="s">
-        <v>795</v>
+        <v>771</v>
       </c>
       <c r="I177">
         <v>2</v>
       </c>
       <c r="J177" t="s">
-        <v>796</v>
+        <v>774</v>
       </c>
       <c r="K177" s="9" t="s">
-        <v>800</v>
+        <v>775</v>
       </c>
       <c r="L177" t="s">
         <v>20</v>
       </c>
       <c r="M177" t="s">
-        <v>796</v>
+        <v>776</v>
       </c>
     </row>
     <row r="178" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A178" s="7" t="s">
-        <v>793</v>
+        <v>763</v>
       </c>
       <c r="B178" t="s">
-        <v>801</v>
+        <v>777</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>795</v>
+        <v>771</v>
       </c>
       <c r="D178" t="s">
-        <v>796</v>
+        <v>772</v>
       </c>
       <c r="G178" t="s">
-        <v>799</v>
+        <v>773</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>795</v>
+        <v>771</v>
       </c>
       <c r="I178">
         <v>2</v>
       </c>
       <c r="J178" t="s">
-        <v>796</v>
+        <v>774</v>
       </c>
       <c r="K178" s="9" t="s">
-        <v>800</v>
+        <v>775</v>
       </c>
       <c r="L178" t="s">
         <v>20</v>
       </c>
       <c r="M178" t="s">
-        <v>796</v>
+        <v>776</v>
       </c>
     </row>
     <row r="179" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>802</v>
+        <v>778</v>
       </c>
       <c r="B179" t="s">
-        <v>803</v>
+        <v>779</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>804</v>
+        <v>780</v>
       </c>
       <c r="D179" t="s">
-        <v>805</v>
+        <v>779</v>
       </c>
       <c r="G179" t="s">
-        <v>806</v>
+        <v>781</v>
       </c>
       <c r="H179" s="3" t="s">
-        <v>804</v>
+        <v>780</v>
       </c>
       <c r="I179">
         <v>2</v>
       </c>
       <c r="J179" t="s">
-        <v>805</v>
+        <v>779</v>
       </c>
       <c r="K179" s="9" t="s">
-        <v>807</v>
+        <v>782</v>
       </c>
       <c r="L179" t="s">
         <v>20</v>
       </c>
       <c r="M179" t="s">
-        <v>805</v>
+        <v>779</v>
       </c>
     </row>
     <row r="180" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A180" s="7" t="s">
-        <v>752</v>
+        <v>783</v>
       </c>
       <c r="B180" t="s">
-        <v>808</v>
+        <v>784</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>774</v>
+        <v>785</v>
       </c>
       <c r="D180" t="s">
-        <v>777</v>
+        <v>786</v>
       </c>
       <c r="E180" t="s">
-        <v>809</v>
+        <v>787</v>
       </c>
       <c r="F180" t="s">
-        <v>810</v>
+        <v>784</v>
       </c>
       <c r="G180" t="s">
-        <v>776</v>
+        <v>788</v>
       </c>
       <c r="H180" s="3" t="s">
-        <v>774</v>
+        <v>785</v>
       </c>
       <c r="I180">
         <v>2</v>
       </c>
       <c r="J180" t="s">
-        <v>777</v>
+        <v>786</v>
       </c>
       <c r="K180" s="9" t="s">
-        <v>778</v>
+        <v>789</v>
       </c>
       <c r="L180" t="s">
         <v>20</v>
       </c>
       <c r="M180" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
-        <v>752</v>
+        <v>790</v>
       </c>
       <c r="B181" t="s">
-        <v>811</v>
+        <v>791</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>812</v>
+        <v>792</v>
       </c>
       <c r="D181" t="s">
-        <v>813</v>
+        <v>793</v>
       </c>
       <c r="E181" t="s">
-        <v>814</v>
+        <v>794</v>
       </c>
       <c r="F181" t="s">
-        <v>815</v>
+        <v>795</v>
       </c>
       <c r="G181" t="s">
-        <v>816</v>
+        <v>796</v>
       </c>
       <c r="H181" s="3" t="s">
-        <v>812</v>
+        <v>792</v>
       </c>
       <c r="I181">
         <v>2</v>
       </c>
       <c r="J181" t="s">
-        <v>813</v>
+        <v>793</v>
       </c>
       <c r="K181" s="9" t="s">
-        <v>690</v>
+        <v>797</v>
       </c>
       <c r="L181" t="s">
         <v>20</v>
       </c>
       <c r="M181" t="s">
-        <v>691</v>
+        <v>793</v>
       </c>
     </row>
     <row r="182" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A182" s="7" t="s">
-        <v>752</v>
+        <v>790</v>
       </c>
       <c r="B182" t="s">
-        <v>817</v>
+        <v>798</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>774</v>
+        <v>792</v>
       </c>
       <c r="D182" t="s">
-        <v>777</v>
+        <v>793</v>
       </c>
       <c r="G182" t="s">
-        <v>776</v>
+        <v>796</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>774</v>
+        <v>792</v>
       </c>
       <c r="I182">
         <v>2</v>
       </c>
       <c r="J182" t="s">
-        <v>777</v>
+        <v>793</v>
       </c>
       <c r="K182" s="9" t="s">
-        <v>778</v>
+        <v>797</v>
       </c>
       <c r="L182" t="s">
         <v>20</v>
       </c>
       <c r="M182" t="s">
-        <v>779</v>
+        <v>793</v>
       </c>
     </row>
     <row r="183" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
-        <v>752</v>
+        <v>799</v>
       </c>
       <c r="B183" t="s">
-        <v>818</v>
+        <v>800</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>774</v>
+        <v>801</v>
       </c>
       <c r="D183" t="s">
-        <v>777</v>
+        <v>802</v>
       </c>
       <c r="G183" t="s">
-        <v>776</v>
+        <v>803</v>
       </c>
       <c r="H183" s="3" t="s">
-        <v>774</v>
+        <v>801</v>
       </c>
       <c r="I183">
         <v>2</v>
       </c>
       <c r="J183" t="s">
-        <v>777</v>
+        <v>802</v>
       </c>
       <c r="K183" s="9" t="s">
-        <v>778</v>
+        <v>804</v>
       </c>
       <c r="L183" t="s">
         <v>20</v>
       </c>
       <c r="M183" t="s">
-        <v>779</v>
+        <v>802</v>
       </c>
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A184" s="7" t="s">
-        <v>819</v>
+        <v>749</v>
       </c>
       <c r="B184" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>821</v>
+        <v>771</v>
       </c>
       <c r="D184" t="s">
-        <v>820</v>
+        <v>774</v>
+      </c>
+      <c r="E184" t="s">
+        <v>806</v>
+      </c>
+      <c r="F184" t="s">
+        <v>807</v>
       </c>
       <c r="G184" t="s">
-        <v>822</v>
+        <v>773</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>821</v>
+        <v>771</v>
       </c>
       <c r="I184">
         <v>2</v>
       </c>
       <c r="J184" t="s">
-        <v>823</v>
+        <v>774</v>
       </c>
       <c r="K184" s="9" t="s">
-        <v>824</v>
+        <v>775</v>
       </c>
       <c r="L184" t="s">
         <v>20</v>
       </c>
       <c r="M184" t="s">
-        <v>823</v>
+        <v>776</v>
       </c>
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
-        <v>825</v>
+        <v>749</v>
       </c>
       <c r="B185" t="s">
-        <v>826</v>
+        <v>808</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>716</v>
+        <v>809</v>
       </c>
       <c r="D185" t="s">
-        <v>717</v>
+        <v>810</v>
       </c>
       <c r="E185" t="s">
-        <v>827</v>
+        <v>811</v>
       </c>
       <c r="F185" t="s">
-        <v>828</v>
+        <v>812</v>
       </c>
       <c r="G185" t="s">
-        <v>720</v>
+        <v>813</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>716</v>
+        <v>809</v>
       </c>
       <c r="I185">
         <v>2</v>
       </c>
       <c r="J185" t="s">
-        <v>717</v>
+        <v>810</v>
       </c>
       <c r="K185" s="9" t="s">
-        <v>721</v>
+        <v>687</v>
       </c>
       <c r="L185" t="s">
         <v>20</v>
       </c>
       <c r="M185" t="s">
-        <v>722</v>
+        <v>688</v>
       </c>
     </row>
     <row r="186" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A186" s="7" t="s">
-        <v>825</v>
+        <v>749</v>
       </c>
       <c r="B186" t="s">
-        <v>829</v>
+        <v>814</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>716</v>
+        <v>771</v>
       </c>
       <c r="D186" t="s">
-        <v>717</v>
-      </c>
-      <c r="E186" t="s">
-        <v>830</v>
-      </c>
-      <c r="F186" t="s">
-        <v>831</v>
+        <v>774</v>
       </c>
       <c r="G186" t="s">
-        <v>720</v>
+        <v>773</v>
       </c>
       <c r="H186" s="3" t="s">
-        <v>716</v>
+        <v>771</v>
       </c>
       <c r="I186">
         <v>2</v>
       </c>
       <c r="J186" t="s">
-        <v>717</v>
+        <v>774</v>
       </c>
       <c r="K186" s="9" t="s">
-        <v>721</v>
+        <v>775</v>
       </c>
       <c r="L186" t="s">
         <v>20</v>
       </c>
       <c r="M186" t="s">
-        <v>722</v>
+        <v>776</v>
       </c>
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
-        <v>832</v>
+        <v>749</v>
       </c>
       <c r="B187" t="s">
-        <v>833</v>
+        <v>815</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>834</v>
+        <v>771</v>
       </c>
       <c r="D187" t="s">
-        <v>835</v>
+        <v>774</v>
       </c>
       <c r="G187" t="s">
-        <v>836</v>
+        <v>773</v>
       </c>
       <c r="H187" s="3" t="s">
-        <v>834</v>
+        <v>771</v>
       </c>
       <c r="I187">
         <v>2</v>
       </c>
       <c r="J187" t="s">
-        <v>835</v>
+        <v>774</v>
       </c>
       <c r="K187" s="9" t="s">
-        <v>690</v>
+        <v>775</v>
       </c>
       <c r="L187" t="s">
         <v>20</v>
       </c>
       <c r="M187" t="s">
-        <v>691</v>
+        <v>776</v>
       </c>
     </row>
     <row r="188" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A188" s="7" t="s">
-        <v>837</v>
+        <v>816</v>
       </c>
       <c r="B188" t="s">
-        <v>838</v>
+        <v>817</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>839</v>
+        <v>818</v>
       </c>
       <c r="D188" t="s">
-        <v>838</v>
+        <v>817</v>
       </c>
       <c r="G188" t="s">
-        <v>840</v>
+        <v>819</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>839</v>
+        <v>818</v>
       </c>
       <c r="I188">
         <v>2</v>
       </c>
       <c r="J188" t="s">
-        <v>838</v>
+        <v>820</v>
       </c>
       <c r="K188" s="9" t="s">
-        <v>319</v>
+        <v>821</v>
       </c>
       <c r="L188" t="s">
         <v>20</v>
       </c>
       <c r="M188" t="s">
-        <v>320</v>
+        <v>820</v>
       </c>
     </row>
     <row r="189" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
-        <v>837</v>
+        <v>822</v>
       </c>
       <c r="B189" t="s">
-        <v>838</v>
+        <v>823</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>339</v>
+        <v>713</v>
       </c>
       <c r="D189" t="s">
-        <v>340</v>
+        <v>714</v>
+      </c>
+      <c r="E189" t="s">
+        <v>824</v>
+      </c>
+      <c r="F189" t="s">
+        <v>825</v>
       </c>
       <c r="G189" t="s">
-        <v>342</v>
+        <v>717</v>
       </c>
       <c r="H189" s="3" t="s">
-        <v>339</v>
+        <v>713</v>
       </c>
       <c r="I189">
         <v>2</v>
       </c>
       <c r="J189" t="s">
-        <v>340</v>
+        <v>714</v>
       </c>
       <c r="K189" s="9" t="s">
-        <v>68</v>
+        <v>718</v>
       </c>
       <c r="L189" t="s">
         <v>20</v>
       </c>
       <c r="M189" t="s">
-        <v>69</v>
+        <v>719</v>
       </c>
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A190" s="7" t="s">
+        <v>822</v>
+      </c>
+      <c r="B190" t="s">
+        <v>826</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D190" t="s">
+        <v>714</v>
+      </c>
+      <c r="E190" t="s">
+        <v>827</v>
+      </c>
+      <c r="F190" t="s">
+        <v>828</v>
+      </c>
+      <c r="G190" t="s">
+        <v>717</v>
+      </c>
+      <c r="H190" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="I190">
+        <v>2</v>
+      </c>
+      <c r="J190" t="s">
+        <v>714</v>
+      </c>
+      <c r="K190" s="9" t="s">
+        <v>718</v>
+      </c>
+      <c r="L190" t="s">
+        <v>20</v>
+      </c>
+      <c r="M190" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A191" s="7" t="s">
+        <v>829</v>
+      </c>
+      <c r="B191" t="s">
+        <v>830</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>831</v>
+      </c>
+      <c r="D191" t="s">
+        <v>832</v>
+      </c>
+      <c r="G191" t="s">
+        <v>833</v>
+      </c>
+      <c r="H191" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="I191">
+        <v>2</v>
+      </c>
+      <c r="J191" t="s">
+        <v>832</v>
+      </c>
+      <c r="K191" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="L191" t="s">
+        <v>20</v>
+      </c>
+      <c r="M191" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A192" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="B192" t="s">
+        <v>835</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>836</v>
+      </c>
+      <c r="D192" t="s">
+        <v>835</v>
+      </c>
+      <c r="G192" t="s">
+        <v>837</v>
+      </c>
+      <c r="H192" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="I192">
+        <v>2</v>
+      </c>
+      <c r="J192" t="s">
+        <v>835</v>
+      </c>
+      <c r="K192" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="L192" t="s">
+        <v>20</v>
+      </c>
+      <c r="M192" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A193" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="B193" t="s">
+        <v>835</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="D193" t="s">
+        <v>338</v>
+      </c>
+      <c r="G193" t="s">
+        <v>340</v>
+      </c>
+      <c r="H193" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="I193">
+        <v>2</v>
+      </c>
+      <c r="J193" t="s">
+        <v>338</v>
+      </c>
+      <c r="K193" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="L193" t="s">
+        <v>20</v>
+      </c>
+      <c r="M193" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A194" s="7" t="s">
+        <v>838</v>
+      </c>
+      <c r="B194" t="s">
+        <v>839</v>
+      </c>
+      <c r="C194" s="5" t="s">
+        <v>840</v>
+      </c>
+      <c r="D194" t="s">
+        <v>839</v>
+      </c>
+      <c r="G194" t="s">
         <v>841</v>
       </c>
-      <c r="B190" t="s">
-        <v>842</v>
-      </c>
-      <c r="C190" s="5" t="s">
-        <v>843</v>
-      </c>
-      <c r="D190" t="s">
-        <v>842</v>
-      </c>
-      <c r="G190" t="s">
-        <v>844</v>
-      </c>
-      <c r="H190" s="3" t="s">
-        <v>843</v>
-      </c>
-      <c r="I190">
-        <v>2</v>
-      </c>
-      <c r="J190" t="s">
-        <v>842</v>
-      </c>
-      <c r="K190" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="L190" t="s">
-        <v>20</v>
-      </c>
-      <c r="M190" t="s">
-        <v>320</v>
+      <c r="H194" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="I194">
+        <v>2</v>
+      </c>
+      <c r="J194" t="s">
+        <v>839</v>
+      </c>
+      <c r="K194" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="L194" t="s">
+        <v>20</v>
+      </c>
+      <c r="M194" t="s">
+        <v>318</v>
       </c>
     </row>
   </sheetData>
